--- a/research/traditional_assets/database/data/croatia/croatia_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/croatia/croatia_oil_gas_distribution.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07937436471013312</v>
+        <v>0.07926839085365489</v>
       </c>
       <c r="C2">
-        <v>876.7675820867028</v>
+        <v>869.0665739913328</v>
       </c>
       <c r="D2">
-        <v>786.8675820867028</v>
+        <v>787.9335739913329</v>
       </c>
       <c r="E2">
-        <v>-16</v>
+        <v>-7.232999999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>8.767000000000001</v>
       </c>
       <c r="G2">
         <v>89.90000000000001</v>
@@ -1451,28 +1451,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4409801</v>
       </c>
       <c r="N2">
-        <v>59.59999999999999</v>
+        <v>59.1590199</v>
       </c>
       <c r="O2">
-        <v>10.728</v>
+        <v>10.648623582</v>
       </c>
       <c r="P2">
-        <v>48.872</v>
+        <v>48.510396318</v>
       </c>
       <c r="Q2">
-        <v>80.872</v>
+        <v>80.51039631800001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07937436471013312</v>
+        <v>0.07965245540773221</v>
       </c>
       <c r="T2">
-        <v>0.5661120226706918</v>
+        <v>0.5708010313433177</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>135.1534910532244</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07926839085365489</v>
+        <v>0.07916241699717665</v>
       </c>
       <c r="C3">
-        <v>869.0665739913328</v>
+        <v>861.3684580732123</v>
       </c>
       <c r="D3">
-        <v>787.9335739913329</v>
+        <v>789.0024580732123</v>
       </c>
       <c r="E3">
-        <v>-7.232999999999999</v>
+        <v>1.534000000000002</v>
       </c>
       <c r="F3">
-        <v>8.767000000000001</v>
+        <v>17.534</v>
       </c>
       <c r="G3">
         <v>89.90000000000001</v>
@@ -1533,28 +1533,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M3">
-        <v>0.4409801</v>
+        <v>0.8819602000000001</v>
       </c>
       <c r="N3">
-        <v>59.1590199</v>
+        <v>58.71803979999999</v>
       </c>
       <c r="O3">
-        <v>10.648623582</v>
+        <v>10.569247164</v>
       </c>
       <c r="P3">
-        <v>48.510396318</v>
+        <v>48.148792636</v>
       </c>
       <c r="Q3">
-        <v>80.51039631800001</v>
+        <v>80.148792636</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07965245540773221</v>
+        <v>0.07993622142569046</v>
       </c>
       <c r="T3">
-        <v>0.5708010313433177</v>
+        <v>0.5755857340704871</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>135.1534910532244</v>
+        <v>67.57674552661219</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07916241699717665</v>
+        <v>0.07905644314069839</v>
       </c>
       <c r="C4">
-        <v>861.3684580732123</v>
+        <v>853.6732461186197</v>
       </c>
       <c r="D4">
-        <v>789.0024580732123</v>
+        <v>790.0742461186197</v>
       </c>
       <c r="E4">
-        <v>1.534000000000002</v>
+        <v>10.301</v>
       </c>
       <c r="F4">
-        <v>17.534</v>
+        <v>26.301</v>
       </c>
       <c r="G4">
         <v>89.90000000000001</v>
@@ -1615,28 +1615,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M4">
-        <v>0.8819602000000001</v>
+        <v>1.3229403</v>
       </c>
       <c r="N4">
-        <v>58.71803979999999</v>
+        <v>58.2770597</v>
       </c>
       <c r="O4">
-        <v>10.569247164</v>
+        <v>10.489870746</v>
       </c>
       <c r="P4">
-        <v>48.148792636</v>
+        <v>47.78718895399999</v>
       </c>
       <c r="Q4">
-        <v>80.148792636</v>
+        <v>79.78718895399999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07993622142569046</v>
+        <v>0.08022583828937979</v>
       </c>
       <c r="T4">
-        <v>0.5755857340704871</v>
+        <v>0.5804690904621341</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>67.57674552661219</v>
+        <v>45.05116368440813</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07905644314069839</v>
+        <v>0.07895046928422016</v>
       </c>
       <c r="C5">
-        <v>853.6732461186197</v>
+        <v>845.9809499779633</v>
       </c>
       <c r="D5">
-        <v>790.0742461186197</v>
+        <v>791.1489499779633</v>
       </c>
       <c r="E5">
-        <v>10.301</v>
+        <v>19.068</v>
       </c>
       <c r="F5">
-        <v>26.301</v>
+        <v>35.068</v>
       </c>
       <c r="G5">
         <v>89.90000000000001</v>
@@ -1697,28 +1697,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M5">
-        <v>1.3229403</v>
+        <v>1.7639204</v>
       </c>
       <c r="N5">
-        <v>58.2770597</v>
+        <v>57.83607959999999</v>
       </c>
       <c r="O5">
-        <v>10.489870746</v>
+        <v>10.410494328</v>
       </c>
       <c r="P5">
-        <v>47.78718895399999</v>
+        <v>47.42558527199999</v>
       </c>
       <c r="Q5">
-        <v>79.78718895399999</v>
+        <v>79.42558527199999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08022583828937979</v>
+        <v>0.08052148883772933</v>
       </c>
       <c r="T5">
-        <v>0.5804690904621341</v>
+        <v>0.5854541834452738</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>45.05116368440813</v>
+        <v>33.78837276330609</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07895046928422016</v>
+        <v>0.07884449542774193</v>
       </c>
       <c r="C6">
-        <v>845.9809499779633</v>
+        <v>838.2915815662177</v>
       </c>
       <c r="D6">
-        <v>791.1489499779633</v>
+        <v>792.2265815662178</v>
       </c>
       <c r="E6">
-        <v>19.068</v>
+        <v>27.83500000000001</v>
       </c>
       <c r="F6">
-        <v>35.068</v>
+        <v>43.83500000000001</v>
       </c>
       <c r="G6">
         <v>89.90000000000001</v>
@@ -1779,28 +1779,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M6">
-        <v>1.7639204</v>
+        <v>2.2049005</v>
       </c>
       <c r="N6">
-        <v>57.83607959999999</v>
+        <v>57.39509949999999</v>
       </c>
       <c r="O6">
-        <v>10.410494328</v>
+        <v>10.33111791</v>
       </c>
       <c r="P6">
-        <v>47.42558527199999</v>
+        <v>47.06398159</v>
       </c>
       <c r="Q6">
-        <v>79.42558527199999</v>
+        <v>79.06398159</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08052148883772933</v>
+        <v>0.0808233636081494</v>
       </c>
       <c r="T6">
-        <v>0.5854541834452738</v>
+        <v>0.5905442257543743</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>33.78837276330609</v>
+        <v>27.03069821064487</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07884449542774193</v>
+        <v>0.07873852157126368</v>
       </c>
       <c r="C7">
-        <v>838.2915815662177</v>
+        <v>830.6051528633644</v>
       </c>
       <c r="D7">
-        <v>792.2265815662178</v>
+        <v>793.3071528633644</v>
       </c>
       <c r="E7">
-        <v>27.83500000000001</v>
+        <v>36.602</v>
       </c>
       <c r="F7">
-        <v>43.83500000000001</v>
+        <v>52.602</v>
       </c>
       <c r="G7">
         <v>89.90000000000001</v>
@@ -1861,28 +1861,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M7">
-        <v>2.2049005</v>
+        <v>2.6458806</v>
       </c>
       <c r="N7">
-        <v>57.39509949999999</v>
+        <v>56.9541194</v>
       </c>
       <c r="O7">
-        <v>10.33111791</v>
+        <v>10.251741492</v>
       </c>
       <c r="P7">
-        <v>47.06398159</v>
+        <v>46.702377908</v>
       </c>
       <c r="Q7">
-        <v>79.06398159</v>
+        <v>78.70237790799999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0808233636081494</v>
+        <v>0.08113166124602519</v>
       </c>
       <c r="T7">
-        <v>0.5905442257543743</v>
+        <v>0.5957425668360089</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>27.03069821064487</v>
+        <v>22.52558184220407</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07873852157126368</v>
+        <v>0.07863254771478544</v>
       </c>
       <c r="C8">
-        <v>830.6051528633644</v>
+        <v>822.9216759148347</v>
       </c>
       <c r="D8">
-        <v>793.3071528633644</v>
+        <v>794.3906759148348</v>
       </c>
       <c r="E8">
-        <v>36.602</v>
+        <v>45.369</v>
       </c>
       <c r="F8">
-        <v>52.602</v>
+        <v>61.369</v>
       </c>
       <c r="G8">
         <v>89.90000000000001</v>
@@ -1943,28 +1943,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M8">
-        <v>2.6458806</v>
+        <v>3.0868607</v>
       </c>
       <c r="N8">
-        <v>56.9541194</v>
+        <v>56.51313929999999</v>
       </c>
       <c r="O8">
-        <v>10.251741492</v>
+        <v>10.172365074</v>
       </c>
       <c r="P8">
-        <v>46.702377908</v>
+        <v>46.34077422599999</v>
       </c>
       <c r="Q8">
-        <v>78.70237790799999</v>
+        <v>78.34077422599999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08113166124602519</v>
+        <v>0.08144658894062951</v>
       </c>
       <c r="T8">
-        <v>0.5957425668360089</v>
+        <v>0.6010527001989689</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.52558184220407</v>
+        <v>19.30764157903205</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07863254771478544</v>
+        <v>0.07852657385830722</v>
       </c>
       <c r="C9">
-        <v>822.9216759148347</v>
+        <v>815.2411628319581</v>
       </c>
       <c r="D9">
-        <v>794.3906759148348</v>
+        <v>795.4771628319581</v>
       </c>
       <c r="E9">
-        <v>45.36900000000001</v>
+        <v>54.13600000000001</v>
       </c>
       <c r="F9">
-        <v>61.36900000000001</v>
+        <v>70.13600000000001</v>
       </c>
       <c r="G9">
         <v>89.90000000000001</v>
@@ -2025,28 +2025,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M9">
-        <v>3.0868607</v>
+        <v>3.5278408</v>
       </c>
       <c r="N9">
-        <v>56.51313929999999</v>
+        <v>56.07215919999999</v>
       </c>
       <c r="O9">
-        <v>10.172365074</v>
+        <v>10.092988656</v>
       </c>
       <c r="P9">
-        <v>46.34077422599999</v>
+        <v>45.979170544</v>
       </c>
       <c r="Q9">
-        <v>78.34077422599999</v>
+        <v>77.979170544</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08144658894062951</v>
+        <v>0.08176836288946436</v>
       </c>
       <c r="T9">
-        <v>0.6010527001989689</v>
+        <v>0.6064782712437325</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.30764157903205</v>
+        <v>16.89418638165305</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07852657385830722</v>
+        <v>0.07842060000182899</v>
       </c>
       <c r="C10">
-        <v>815.2411628319581</v>
+        <v>807.5636257924139</v>
       </c>
       <c r="D10">
-        <v>795.4771628319581</v>
+        <v>796.5666257924139</v>
       </c>
       <c r="E10">
-        <v>54.13600000000001</v>
+        <v>62.90300000000001</v>
       </c>
       <c r="F10">
-        <v>70.13600000000001</v>
+        <v>78.90300000000001</v>
       </c>
       <c r="G10">
         <v>89.90000000000001</v>
@@ -2107,28 +2107,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M10">
-        <v>3.5278408</v>
+        <v>3.9688209</v>
       </c>
       <c r="N10">
-        <v>56.07215919999999</v>
+        <v>55.6311791</v>
       </c>
       <c r="O10">
-        <v>10.092988656</v>
+        <v>10.013612238</v>
       </c>
       <c r="P10">
-        <v>45.979170544</v>
+        <v>45.617566862</v>
       </c>
       <c r="Q10">
-        <v>77.979170544</v>
+        <v>77.61756686199999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08176836288946436</v>
+        <v>0.08209720879321866</v>
       </c>
       <c r="T10">
-        <v>0.6064782712437325</v>
+        <v>0.6120230856081612</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.89418638165305</v>
+        <v>15.01705456146938</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07842060000182899</v>
+        <v>0.07831462614535073</v>
       </c>
       <c r="C11">
-        <v>807.5636257924139</v>
+        <v>799.8890770406856</v>
       </c>
       <c r="D11">
-        <v>796.5666257924139</v>
+        <v>797.6590770406856</v>
       </c>
       <c r="E11">
-        <v>62.90300000000001</v>
+        <v>71.67</v>
       </c>
       <c r="F11">
-        <v>78.90300000000001</v>
+        <v>87.67</v>
       </c>
       <c r="G11">
         <v>89.90000000000001</v>
@@ -2189,28 +2189,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M11">
-        <v>3.9688209</v>
+        <v>4.409801</v>
       </c>
       <c r="N11">
-        <v>55.6311791</v>
+        <v>55.19019899999999</v>
       </c>
       <c r="O11">
-        <v>10.013612238</v>
+        <v>9.934235819999998</v>
       </c>
       <c r="P11">
-        <v>45.617566862</v>
+        <v>45.25596317999999</v>
       </c>
       <c r="Q11">
-        <v>77.61756686199999</v>
+        <v>77.25596317999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08209720879321866</v>
+        <v>0.08243336238372304</v>
       </c>
       <c r="T11">
-        <v>0.6120230856081612</v>
+        <v>0.6176911180695771</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.01705456146938</v>
+        <v>13.51534910532244</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07831462614535074</v>
+        <v>0.07834395228887249</v>
       </c>
       <c r="C12">
-        <v>799.8890770406856</v>
+        <v>790.8194632649574</v>
       </c>
       <c r="D12">
-        <v>797.6590770406856</v>
+        <v>797.3564632649575</v>
       </c>
       <c r="E12">
-        <v>71.67000000000002</v>
+        <v>80.43700000000001</v>
       </c>
       <c r="F12">
-        <v>87.67000000000002</v>
+        <v>96.43700000000001</v>
       </c>
       <c r="G12">
         <v>89.90000000000001</v>
@@ -2271,45 +2271,45 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M12">
-        <v>4.409801000000001</v>
+        <v>4.995436600000001</v>
       </c>
       <c r="N12">
-        <v>55.19019899999999</v>
+        <v>54.6045634</v>
       </c>
       <c r="O12">
-        <v>9.934235819999998</v>
+        <v>9.828821411999998</v>
       </c>
       <c r="P12">
-        <v>45.25596317999999</v>
+        <v>44.775741988</v>
       </c>
       <c r="Q12">
-        <v>77.25596317999999</v>
+        <v>76.77574198799999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08243336238372304</v>
+        <v>0.08277706998749718</v>
       </c>
       <c r="T12">
-        <v>0.6176911180695771</v>
+        <v>0.6234865220469799</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.18</v>
       </c>
       <c r="W12">
-        <v>0.041246</v>
+        <v>0.042476</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.51534910532244</v>
+        <v>11.93088908384905</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07834395228887249</v>
+        <v>0.07825027843239425</v>
       </c>
       <c r="C13">
-        <v>790.8194632649574</v>
+        <v>783.0198807842842</v>
       </c>
       <c r="D13">
-        <v>797.3564632649575</v>
+        <v>798.3238807842843</v>
       </c>
       <c r="E13">
-        <v>80.43700000000001</v>
+        <v>89.20400000000001</v>
       </c>
       <c r="F13">
-        <v>96.43700000000001</v>
+        <v>105.204</v>
       </c>
       <c r="G13">
         <v>89.90000000000001</v>
@@ -2353,28 +2353,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M13">
-        <v>4.995436600000001</v>
+        <v>5.449567200000001</v>
       </c>
       <c r="N13">
-        <v>54.6045634</v>
+        <v>54.15043279999999</v>
       </c>
       <c r="O13">
-        <v>9.828821411999998</v>
+        <v>9.747077903999998</v>
       </c>
       <c r="P13">
-        <v>44.775741988</v>
+        <v>44.403354896</v>
       </c>
       <c r="Q13">
-        <v>76.77574198799999</v>
+        <v>76.403354896</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08277706998749718</v>
+        <v>0.08312858912772074</v>
       </c>
       <c r="T13">
-        <v>0.6234865220469799</v>
+        <v>0.629413639751142</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.93088908384905</v>
+        <v>10.93664832686162</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07825027843239425</v>
+        <v>0.078156604575916</v>
       </c>
       <c r="C14">
-        <v>783.0198807842842</v>
+        <v>775.2226486540123</v>
       </c>
       <c r="D14">
-        <v>798.3238807842843</v>
+        <v>799.2936486540124</v>
       </c>
       <c r="E14">
-        <v>89.20400000000001</v>
+        <v>97.971</v>
       </c>
       <c r="F14">
-        <v>105.204</v>
+        <v>113.971</v>
       </c>
       <c r="G14">
         <v>89.90000000000001</v>
@@ -2435,28 +2435,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M14">
-        <v>5.449567200000001</v>
+        <v>5.9036978</v>
       </c>
       <c r="N14">
-        <v>54.15043279999999</v>
+        <v>53.69630219999999</v>
       </c>
       <c r="O14">
-        <v>9.747077903999998</v>
+        <v>9.665334395999999</v>
       </c>
       <c r="P14">
-        <v>44.403354896</v>
+        <v>44.03096780399999</v>
       </c>
       <c r="Q14">
-        <v>76.403354896</v>
+        <v>76.030967804</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08312858912772074</v>
+        <v>0.08348818916771955</v>
       </c>
       <c r="T14">
-        <v>0.629413639751142</v>
+        <v>0.63547701303471</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.93664832686162</v>
+        <v>10.09536768633381</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.078156604575916</v>
+        <v>0.07825809071943778</v>
       </c>
       <c r="C15">
-        <v>775.2226486540123</v>
+        <v>765.4051096095521</v>
       </c>
       <c r="D15">
-        <v>799.2936486540124</v>
+        <v>798.2431096095522</v>
       </c>
       <c r="E15">
-        <v>97.971</v>
+        <v>106.738</v>
       </c>
       <c r="F15">
-        <v>113.971</v>
+        <v>122.738</v>
       </c>
       <c r="G15">
         <v>89.90000000000001</v>
@@ -2517,45 +2517,45 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M15">
-        <v>5.9036978</v>
+        <v>6.566483000000001</v>
       </c>
       <c r="N15">
-        <v>53.69630219999999</v>
+        <v>53.033517</v>
       </c>
       <c r="O15">
-        <v>9.665334395999999</v>
+        <v>9.546033059999999</v>
       </c>
       <c r="P15">
-        <v>44.03096780399999</v>
+        <v>43.48748394</v>
       </c>
       <c r="Q15">
-        <v>76.030967804</v>
+        <v>75.48748394</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08348818916771955</v>
+        <v>0.08385615199934625</v>
       </c>
       <c r="T15">
-        <v>0.63547701303471</v>
+        <v>0.6416813949992912</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.18</v>
       </c>
       <c r="W15">
-        <v>0.042476</v>
+        <v>0.04387</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.09536768633381</v>
+        <v>9.076395994629086</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07825809071943778</v>
+        <v>0.07817835686295953</v>
       </c>
       <c r="C16">
-        <v>765.4051096095521</v>
+        <v>757.4632459777189</v>
       </c>
       <c r="D16">
-        <v>798.2431096095522</v>
+        <v>799.0682459777189</v>
       </c>
       <c r="E16">
-        <v>106.738</v>
+        <v>115.505</v>
       </c>
       <c r="F16">
-        <v>122.738</v>
+        <v>131.505</v>
       </c>
       <c r="G16">
         <v>89.90000000000001</v>
@@ -2599,28 +2599,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M16">
-        <v>6.566483000000001</v>
+        <v>7.035517500000001</v>
       </c>
       <c r="N16">
-        <v>53.033517</v>
+        <v>52.5644825</v>
       </c>
       <c r="O16">
-        <v>9.546033059999999</v>
+        <v>9.461606849999999</v>
       </c>
       <c r="P16">
-        <v>43.48748394</v>
+        <v>43.10287565</v>
       </c>
       <c r="Q16">
-        <v>75.48748394</v>
+        <v>75.10287565</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08385615199934625</v>
+        <v>0.08423277277995239</v>
       </c>
       <c r="T16">
-        <v>0.6416813949992912</v>
+        <v>0.6480317624218626</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.076395994629086</v>
+        <v>8.47130292832048</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07817835686295953</v>
+        <v>0.07809862300648129</v>
       </c>
       <c r="C17">
-        <v>757.4632459777189</v>
+        <v>749.5230899824045</v>
       </c>
       <c r="D17">
-        <v>799.0682459777189</v>
+        <v>799.8950899824046</v>
       </c>
       <c r="E17">
-        <v>115.505</v>
+        <v>124.272</v>
       </c>
       <c r="F17">
-        <v>131.505</v>
+        <v>140.272</v>
       </c>
       <c r="G17">
         <v>89.90000000000001</v>
@@ -2681,28 +2681,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M17">
-        <v>7.035517499999999</v>
+        <v>7.504552000000001</v>
       </c>
       <c r="N17">
-        <v>52.5644825</v>
+        <v>52.09544799999999</v>
       </c>
       <c r="O17">
-        <v>9.461606849999999</v>
+        <v>9.377180639999997</v>
       </c>
       <c r="P17">
-        <v>43.10287565</v>
+        <v>42.71826735999999</v>
       </c>
       <c r="Q17">
-        <v>75.10287565</v>
+        <v>74.71826736</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08423277277995239</v>
+        <v>0.08461836072200155</v>
       </c>
       <c r="T17">
-        <v>0.6480317624218626</v>
+        <v>0.6545333290687808</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.471302928320483</v>
+        <v>7.94184649530045</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07809862300648129</v>
+        <v>0.07813040915000306</v>
       </c>
       <c r="C18">
-        <v>749.5230899824045</v>
+        <v>740.4262610903073</v>
       </c>
       <c r="D18">
-        <v>799.8950899824046</v>
+        <v>799.5652610903073</v>
       </c>
       <c r="E18">
-        <v>124.272</v>
+        <v>133.039</v>
       </c>
       <c r="F18">
-        <v>140.272</v>
+        <v>149.039</v>
       </c>
       <c r="G18">
         <v>89.90000000000001</v>
@@ -2763,45 +2763,45 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M18">
-        <v>7.504552000000001</v>
+        <v>8.092817700000001</v>
       </c>
       <c r="N18">
-        <v>52.09544799999999</v>
+        <v>51.5071823</v>
       </c>
       <c r="O18">
-        <v>9.377180639999997</v>
+        <v>9.271292813999999</v>
       </c>
       <c r="P18">
-        <v>42.71826735999999</v>
+        <v>42.235889486</v>
       </c>
       <c r="Q18">
-        <v>74.71826736</v>
+        <v>74.23588948599999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08461836072200155</v>
+        <v>0.08501323993976272</v>
       </c>
       <c r="T18">
-        <v>0.6545333290687808</v>
+        <v>0.6611915599722514</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.18</v>
       </c>
       <c r="W18">
-        <v>0.04387</v>
+        <v>0.044526</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.94184649530045</v>
+        <v>7.364554869436883</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07813040915000306</v>
+        <v>0.0780572352935248</v>
       </c>
       <c r="C19">
-        <v>740.4262610903073</v>
+        <v>732.4189575972501</v>
       </c>
       <c r="D19">
-        <v>799.5652610903073</v>
+        <v>800.3249575972502</v>
       </c>
       <c r="E19">
-        <v>133.039</v>
+        <v>141.806</v>
       </c>
       <c r="F19">
-        <v>149.039</v>
+        <v>157.806</v>
       </c>
       <c r="G19">
         <v>89.90000000000001</v>
@@ -2845,28 +2845,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M19">
-        <v>8.092817700000001</v>
+        <v>8.568865800000003</v>
       </c>
       <c r="N19">
-        <v>51.5071823</v>
+        <v>51.03113419999999</v>
       </c>
       <c r="O19">
-        <v>9.271292813999999</v>
+        <v>9.185604155999998</v>
       </c>
       <c r="P19">
-        <v>42.235889486</v>
+        <v>41.84553004399999</v>
       </c>
       <c r="Q19">
-        <v>74.23588948599999</v>
+        <v>73.84553004399999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08501323993976272</v>
+        <v>0.0854177503579571</v>
       </c>
       <c r="T19">
-        <v>0.6611915599722514</v>
+        <v>0.6680121867514165</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.364554869436883</v>
+        <v>6.955412932245943</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0780572352935248</v>
+        <v>0.07798406143704657</v>
       </c>
       <c r="C20">
-        <v>732.4189575972501</v>
+        <v>724.4130991086053</v>
       </c>
       <c r="D20">
-        <v>800.3249575972502</v>
+        <v>801.0860991086053</v>
       </c>
       <c r="E20">
-        <v>141.806</v>
+        <v>150.573</v>
       </c>
       <c r="F20">
-        <v>157.806</v>
+        <v>166.573</v>
       </c>
       <c r="G20">
         <v>89.90000000000001</v>
@@ -2927,28 +2927,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M20">
-        <v>8.568865800000001</v>
+        <v>9.044913900000001</v>
       </c>
       <c r="N20">
-        <v>51.0311342</v>
+        <v>50.5550861</v>
       </c>
       <c r="O20">
-        <v>9.185604155999998</v>
+        <v>9.099915498</v>
       </c>
       <c r="P20">
-        <v>41.845530044</v>
+        <v>41.455170602</v>
       </c>
       <c r="Q20">
-        <v>73.845530044</v>
+        <v>73.455170602</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08541775035795708</v>
+        <v>0.08583224868771182</v>
       </c>
       <c r="T20">
-        <v>0.6680121867514163</v>
+        <v>0.6750012240683385</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.955412932245944</v>
+        <v>6.589338567390895</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07798406143704657</v>
+        <v>0.07791088758056834</v>
       </c>
       <c r="C21">
-        <v>724.4130991086053</v>
+        <v>716.4086897510706</v>
       </c>
       <c r="D21">
-        <v>801.0860991086053</v>
+        <v>801.8486897510707</v>
       </c>
       <c r="E21">
-        <v>150.573</v>
+        <v>159.34</v>
       </c>
       <c r="F21">
-        <v>166.573</v>
+        <v>175.34</v>
       </c>
       <c r="G21">
         <v>89.90000000000001</v>
@@ -3009,28 +3009,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M21">
-        <v>9.044913900000001</v>
+        <v>9.520962000000003</v>
       </c>
       <c r="N21">
-        <v>50.5550861</v>
+        <v>50.07903799999999</v>
       </c>
       <c r="O21">
-        <v>9.099915498</v>
+        <v>9.014226839999997</v>
       </c>
       <c r="P21">
-        <v>41.455170602</v>
+        <v>41.06481115999999</v>
       </c>
       <c r="Q21">
-        <v>73.455170602</v>
+        <v>73.06481115999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08583224868771182</v>
+        <v>0.08625710947571041</v>
       </c>
       <c r="T21">
-        <v>0.6750012240683385</v>
+        <v>0.6821649873181836</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.589338567390895</v>
+        <v>6.259871639021348</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07791088758056834</v>
+        <v>0.07800991372409009</v>
       </c>
       <c r="C22">
-        <v>716.4086897510706</v>
+        <v>706.6100228568009</v>
       </c>
       <c r="D22">
-        <v>801.8486897510707</v>
+        <v>800.8170228568009</v>
       </c>
       <c r="E22">
-        <v>159.34</v>
+        <v>168.107</v>
       </c>
       <c r="F22">
-        <v>175.34</v>
+        <v>184.107</v>
       </c>
       <c r="G22">
         <v>89.90000000000001</v>
@@ -3091,45 +3091,45 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M22">
-        <v>9.520962000000003</v>
+        <v>10.1811171</v>
       </c>
       <c r="N22">
-        <v>50.07903799999999</v>
+        <v>49.41888289999999</v>
       </c>
       <c r="O22">
-        <v>9.014226839999997</v>
+        <v>8.895398921999998</v>
       </c>
       <c r="P22">
-        <v>41.06481115999999</v>
+        <v>40.52348397799999</v>
       </c>
       <c r="Q22">
-        <v>73.06481115999999</v>
+        <v>72.523483978</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08625710947571041</v>
+        <v>0.08669272623302543</v>
       </c>
       <c r="T22">
-        <v>0.6821649873181836</v>
+        <v>0.6895101116629616</v>
       </c>
       <c r="U22">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.18</v>
       </c>
       <c r="W22">
-        <v>0.044526</v>
+        <v>0.045346</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.259871639021348</v>
+        <v>5.853974511303871</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07800991372409009</v>
+        <v>0.07794493986761186</v>
       </c>
       <c r="C23">
-        <v>706.6100228568009</v>
+        <v>698.5196289798272</v>
       </c>
       <c r="D23">
-        <v>800.8170228568009</v>
+        <v>801.4936289798272</v>
       </c>
       <c r="E23">
-        <v>168.107</v>
+        <v>176.874</v>
       </c>
       <c r="F23">
-        <v>184.107</v>
+        <v>192.874</v>
       </c>
       <c r="G23">
         <v>89.90000000000001</v>
@@ -3173,28 +3173,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M23">
-        <v>10.1811171</v>
+        <v>10.6659322</v>
       </c>
       <c r="N23">
-        <v>49.41888289999999</v>
+        <v>48.93406779999999</v>
       </c>
       <c r="O23">
-        <v>8.895398921999998</v>
+        <v>8.808132203999998</v>
       </c>
       <c r="P23">
-        <v>40.52348397799999</v>
+        <v>40.125935596</v>
       </c>
       <c r="Q23">
-        <v>72.523483978</v>
+        <v>72.12593559600001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08669272623302543</v>
+        <v>0.08713951265078443</v>
       </c>
       <c r="T23">
-        <v>0.6895101116629616</v>
+        <v>0.6970435725294005</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.853974511303872</v>
+        <v>5.587884760790058</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07794493986761186</v>
+        <v>0.07787996601113362</v>
       </c>
       <c r="C24">
-        <v>698.5196289798272</v>
+        <v>690.430379391621</v>
       </c>
       <c r="D24">
-        <v>801.4936289798272</v>
+        <v>802.1713793916211</v>
       </c>
       <c r="E24">
-        <v>176.874</v>
+        <v>185.641</v>
       </c>
       <c r="F24">
-        <v>192.874</v>
+        <v>201.641</v>
       </c>
       <c r="G24">
         <v>89.90000000000001</v>
@@ -3255,28 +3255,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M24">
-        <v>10.6659322</v>
+        <v>11.1507473</v>
       </c>
       <c r="N24">
-        <v>48.93406779999999</v>
+        <v>48.4492527</v>
       </c>
       <c r="O24">
-        <v>8.808132203999998</v>
+        <v>8.720865485999999</v>
       </c>
       <c r="P24">
-        <v>40.125935596</v>
+        <v>39.72838721399999</v>
       </c>
       <c r="Q24">
-        <v>72.12593559600001</v>
+        <v>71.72838721399999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08713951265078443</v>
+        <v>0.08759790391056313</v>
       </c>
       <c r="T24">
-        <v>0.6970435725294005</v>
+        <v>0.7047727077040588</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.587884760790058</v>
+        <v>5.344933249451361</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07787996601113362</v>
+        <v>0.07781499215465539</v>
       </c>
       <c r="C25">
-        <v>690.430379391621</v>
+        <v>682.3422769975027</v>
       </c>
       <c r="D25">
-        <v>802.1713793916211</v>
+        <v>802.8502769975028</v>
       </c>
       <c r="E25">
-        <v>185.641</v>
+        <v>194.408</v>
       </c>
       <c r="F25">
-        <v>201.641</v>
+        <v>210.408</v>
       </c>
       <c r="G25">
         <v>89.90000000000001</v>
@@ -3337,28 +3337,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M25">
-        <v>11.1507473</v>
+        <v>11.6355624</v>
       </c>
       <c r="N25">
-        <v>48.4492527</v>
+        <v>47.9644376</v>
       </c>
       <c r="O25">
-        <v>8.720865485999999</v>
+        <v>8.633598767999999</v>
       </c>
       <c r="P25">
-        <v>39.72838721399999</v>
+        <v>39.330838832</v>
       </c>
       <c r="Q25">
-        <v>71.72838721399999</v>
+        <v>71.330838832</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08759790391056313</v>
+        <v>0.08806835809823077</v>
       </c>
       <c r="T25">
-        <v>0.7047727077040588</v>
+        <v>0.7127052411727869</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.344933249451361</v>
+        <v>5.122227697390888</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07781499215465537</v>
+        <v>0.07775001829817714</v>
       </c>
       <c r="C26">
-        <v>682.3422769975029</v>
+        <v>674.2553247126364</v>
       </c>
       <c r="D26">
-        <v>802.850276997503</v>
+        <v>803.5303247126365</v>
       </c>
       <c r="E26">
-        <v>194.408</v>
+        <v>203.175</v>
       </c>
       <c r="F26">
-        <v>210.408</v>
+        <v>219.175</v>
       </c>
       <c r="G26">
         <v>89.90000000000001</v>
@@ -3419,28 +3419,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M26">
-        <v>11.6355624</v>
+        <v>12.1203775</v>
       </c>
       <c r="N26">
-        <v>47.9644376</v>
+        <v>47.47962249999999</v>
       </c>
       <c r="O26">
-        <v>8.633598767999999</v>
+        <v>8.546332049999998</v>
       </c>
       <c r="P26">
-        <v>39.330838832</v>
+        <v>38.93329044999999</v>
       </c>
       <c r="Q26">
-        <v>71.330838832</v>
+        <v>70.93329044999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08806835809823076</v>
+        <v>0.08855135773090285</v>
       </c>
       <c r="T26">
-        <v>0.7127052411727868</v>
+        <v>0.7208493088673477</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.122227697390888</v>
+        <v>4.917338589495252</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07775001829817714</v>
+        <v>0.07768504444169889</v>
       </c>
       <c r="C27">
-        <v>674.2553247126364</v>
+        <v>666.1695254620714</v>
       </c>
       <c r="D27">
-        <v>803.5303247126365</v>
+        <v>804.2115254620714</v>
       </c>
       <c r="E27">
-        <v>203.175</v>
+        <v>211.942</v>
       </c>
       <c r="F27">
-        <v>219.175</v>
+        <v>227.942</v>
       </c>
       <c r="G27">
         <v>89.90000000000001</v>
@@ -3501,28 +3501,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M27">
-        <v>12.1203775</v>
+        <v>12.6051926</v>
       </c>
       <c r="N27">
-        <v>47.47962249999999</v>
+        <v>46.99480739999999</v>
       </c>
       <c r="O27">
-        <v>8.546332049999998</v>
+        <v>8.459065331999998</v>
       </c>
       <c r="P27">
-        <v>38.93329044999999</v>
+        <v>38.53574206799999</v>
       </c>
       <c r="Q27">
-        <v>70.93329044999999</v>
+        <v>70.53574206799999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08855135773090285</v>
+        <v>0.08904741140770121</v>
       </c>
       <c r="T27">
-        <v>0.7208493088673477</v>
+        <v>0.7292134864995993</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.917338589495252</v>
+        <v>4.728210182206974</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07768504444169889</v>
+        <v>0.07762007058522066</v>
       </c>
       <c r="C28">
-        <v>666.1695254620714</v>
+        <v>658.0848821807837</v>
       </c>
       <c r="D28">
-        <v>804.2115254620714</v>
+        <v>804.8938821807837</v>
       </c>
       <c r="E28">
-        <v>211.942</v>
+        <v>220.709</v>
       </c>
       <c r="F28">
-        <v>227.942</v>
+        <v>236.709</v>
       </c>
       <c r="G28">
         <v>89.90000000000001</v>
@@ -3583,28 +3583,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M28">
-        <v>12.6051926</v>
+        <v>13.0900077</v>
       </c>
       <c r="N28">
-        <v>46.99480739999999</v>
+        <v>46.50999229999999</v>
       </c>
       <c r="O28">
-        <v>8.459065331999998</v>
+        <v>8.371798613999999</v>
       </c>
       <c r="P28">
-        <v>38.53574206799999</v>
+        <v>38.13819368599999</v>
       </c>
       <c r="Q28">
-        <v>70.53574206799999</v>
+        <v>70.13819368599999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08904741140770121</v>
+        <v>0.08955705559619268</v>
       </c>
       <c r="T28">
-        <v>0.7292134864995993</v>
+        <v>0.7378068196834194</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.728210182206974</v>
+        <v>4.553091286569678</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07762007058522066</v>
+        <v>0.07812909672874242</v>
       </c>
       <c r="C29">
-        <v>658.0848821807837</v>
+        <v>644.002874044813</v>
       </c>
       <c r="D29">
-        <v>804.8938821807837</v>
+        <v>799.578874044813</v>
       </c>
       <c r="E29">
-        <v>220.709</v>
+        <v>229.476</v>
       </c>
       <c r="F29">
-        <v>236.709</v>
+        <v>245.476</v>
       </c>
       <c r="G29">
         <v>89.90000000000001</v>
@@ -3665,45 +3665,45 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M29">
-        <v>13.0900077</v>
+        <v>14.1885128</v>
       </c>
       <c r="N29">
-        <v>46.50999229999999</v>
+        <v>45.41148719999999</v>
       </c>
       <c r="O29">
-        <v>8.371798613999999</v>
+        <v>8.174067695999998</v>
       </c>
       <c r="P29">
-        <v>38.13819368599999</v>
+        <v>37.23741950399999</v>
       </c>
       <c r="Q29">
-        <v>70.13819368599999</v>
+        <v>69.23741950399999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08955705559619268</v>
+        <v>0.09008085656769781</v>
       </c>
       <c r="T29">
-        <v>0.7378068196834194</v>
+        <v>0.7466388565667903</v>
       </c>
       <c r="U29">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V29">
         <v>0.18</v>
       </c>
       <c r="W29">
-        <v>0.045346</v>
+        <v>0.04739600000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.553091286569678</v>
+        <v>4.200581191285952</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07812909672874242</v>
+        <v>0.07808462287226417</v>
       </c>
       <c r="C30">
-        <v>644.002874044813</v>
+        <v>635.6974487000497</v>
       </c>
       <c r="D30">
-        <v>799.578874044813</v>
+        <v>800.0404487000498</v>
       </c>
       <c r="E30">
-        <v>229.476</v>
+        <v>238.2430000000001</v>
       </c>
       <c r="F30">
-        <v>245.476</v>
+        <v>254.2430000000001</v>
       </c>
       <c r="G30">
         <v>89.90000000000001</v>
@@ -3747,28 +3747,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M30">
-        <v>14.1885128</v>
+        <v>14.6952454</v>
       </c>
       <c r="N30">
-        <v>45.41148719999999</v>
+        <v>44.90475459999999</v>
       </c>
       <c r="O30">
-        <v>8.174067695999998</v>
+        <v>8.082855827999998</v>
       </c>
       <c r="P30">
-        <v>37.23741950399999</v>
+        <v>36.82189877199999</v>
       </c>
       <c r="Q30">
-        <v>69.23741950399999</v>
+        <v>68.821898772</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09008085656769781</v>
+        <v>0.09061941249614672</v>
       </c>
       <c r="T30">
-        <v>0.7466388565667903</v>
+        <v>0.7557196832215235</v>
       </c>
       <c r="U30">
         <v>0.0578</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.200581191285952</v>
+        <v>4.05573356400023</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07808462287226417</v>
+        <v>0.07890114901578593</v>
       </c>
       <c r="C31">
-        <v>635.6974487000498</v>
+        <v>618.5401151413228</v>
       </c>
       <c r="D31">
-        <v>800.0404487000498</v>
+        <v>791.6501151413228</v>
       </c>
       <c r="E31">
-        <v>238.243</v>
+        <v>247.01</v>
       </c>
       <c r="F31">
-        <v>254.243</v>
+        <v>263.01</v>
       </c>
       <c r="G31">
         <v>89.90000000000001</v>
@@ -3829,45 +3829,45 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M31">
-        <v>14.6952454</v>
+        <v>16.122513</v>
       </c>
       <c r="N31">
-        <v>44.90475459999999</v>
+        <v>43.477487</v>
       </c>
       <c r="O31">
-        <v>8.082855827999998</v>
+        <v>7.825947659999999</v>
       </c>
       <c r="P31">
-        <v>36.82189877199999</v>
+        <v>35.65153934</v>
       </c>
       <c r="Q31">
-        <v>68.821898772</v>
+        <v>67.65153934</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09061941249614672</v>
+        <v>0.09117335573683705</v>
       </c>
       <c r="T31">
-        <v>0.7557196832215235</v>
+        <v>0.765059962066392</v>
       </c>
       <c r="U31">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V31">
         <v>0.18</v>
       </c>
       <c r="W31">
-        <v>0.04739600000000001</v>
+        <v>0.05026600000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.05573356400023</v>
+        <v>3.696694181608041</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07890114901578593</v>
+        <v>0.0788853751593077</v>
       </c>
       <c r="C32">
-        <v>618.5401151413228</v>
+        <v>609.9335343418632</v>
       </c>
       <c r="D32">
-        <v>791.6501151413228</v>
+        <v>791.8105343418631</v>
       </c>
       <c r="E32">
-        <v>247.01</v>
+        <v>255.777</v>
       </c>
       <c r="F32">
-        <v>263.01</v>
+        <v>271.777</v>
       </c>
       <c r="G32">
         <v>89.90000000000001</v>
@@ -3911,28 +3911,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M32">
-        <v>16.122513</v>
+        <v>16.6599301</v>
       </c>
       <c r="N32">
-        <v>43.477487</v>
+        <v>42.9400699</v>
       </c>
       <c r="O32">
-        <v>7.825947659999999</v>
+        <v>7.729212581999999</v>
       </c>
       <c r="P32">
-        <v>35.65153934</v>
+        <v>35.210857318</v>
       </c>
       <c r="Q32">
-        <v>67.65153934</v>
+        <v>67.210857318</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09117335573683705</v>
+        <v>0.09174335530334449</v>
       </c>
       <c r="T32">
-        <v>0.765059962066392</v>
+        <v>0.7746709736314018</v>
       </c>
       <c r="U32">
         <v>0.0613</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.696694181608041</v>
+        <v>3.57744598220133</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0788853751593077</v>
+        <v>0.07960432130282945</v>
       </c>
       <c r="C33">
-        <v>609.9335343418632</v>
+        <v>593.9203378670784</v>
       </c>
       <c r="D33">
-        <v>791.8105343418631</v>
+        <v>784.5643378670784</v>
       </c>
       <c r="E33">
-        <v>255.777</v>
+        <v>264.544</v>
       </c>
       <c r="F33">
-        <v>271.777</v>
+        <v>280.544</v>
       </c>
       <c r="G33">
         <v>89.90000000000001</v>
@@ -3993,45 +3993,45 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M33">
-        <v>16.6599301</v>
+        <v>17.9828704</v>
       </c>
       <c r="N33">
-        <v>42.9400699</v>
+        <v>41.61712959999999</v>
       </c>
       <c r="O33">
-        <v>7.729212581999999</v>
+        <v>7.491083327999998</v>
       </c>
       <c r="P33">
-        <v>35.210857318</v>
+        <v>34.126046272</v>
       </c>
       <c r="Q33">
-        <v>67.210857318</v>
+        <v>66.126046272</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09174335530334449</v>
+        <v>0.09233011956298449</v>
       </c>
       <c r="T33">
-        <v>0.7746709736314018</v>
+        <v>0.784564662007147</v>
       </c>
       <c r="U33">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V33">
         <v>0.18</v>
       </c>
       <c r="W33">
-        <v>0.05026600000000001</v>
+        <v>0.052562</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.57744598220133</v>
+        <v>3.314265113093402</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07960432130282945</v>
+        <v>0.07961150744635122</v>
       </c>
       <c r="C34">
-        <v>593.9203378670784</v>
+        <v>585.0815787316136</v>
       </c>
       <c r="D34">
-        <v>784.5643378670784</v>
+        <v>784.4925787316137</v>
       </c>
       <c r="E34">
-        <v>264.544</v>
+        <v>273.311</v>
       </c>
       <c r="F34">
-        <v>280.544</v>
+        <v>289.311</v>
       </c>
       <c r="G34">
         <v>89.90000000000001</v>
@@ -4075,28 +4075,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M34">
-        <v>17.9828704</v>
+        <v>18.5448351</v>
       </c>
       <c r="N34">
-        <v>41.61712959999999</v>
+        <v>41.05516489999999</v>
       </c>
       <c r="O34">
-        <v>7.491083327999998</v>
+        <v>7.389929681999998</v>
       </c>
       <c r="P34">
-        <v>34.126046272</v>
+        <v>33.66523521799999</v>
       </c>
       <c r="Q34">
-        <v>66.126046272</v>
+        <v>65.66523521799999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09233011956298449</v>
+        <v>0.09293439917365853</v>
       </c>
       <c r="T34">
-        <v>0.784564662007147</v>
+        <v>0.7947536843642579</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.314265113093402</v>
+        <v>3.213832836939056</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07961150744635122</v>
+        <v>0.07961869358987297</v>
       </c>
       <c r="C35">
-        <v>585.0815787316136</v>
+        <v>576.2428327216567</v>
       </c>
       <c r="D35">
-        <v>784.4925787316137</v>
+        <v>784.4208327216567</v>
       </c>
       <c r="E35">
-        <v>273.311</v>
+        <v>282.078</v>
       </c>
       <c r="F35">
-        <v>289.311</v>
+        <v>298.078</v>
       </c>
       <c r="G35">
         <v>89.90000000000001</v>
@@ -4157,28 +4157,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M35">
-        <v>18.5448351</v>
+        <v>19.1067998</v>
       </c>
       <c r="N35">
-        <v>41.05516489999999</v>
+        <v>40.49320019999999</v>
       </c>
       <c r="O35">
-        <v>7.389929681999998</v>
+        <v>7.288776035999998</v>
       </c>
       <c r="P35">
-        <v>33.66523521799999</v>
+        <v>33.20442416399999</v>
       </c>
       <c r="Q35">
-        <v>65.66523521799999</v>
+        <v>65.20442416399999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09293439917365853</v>
+        <v>0.09355699028768633</v>
       </c>
       <c r="T35">
-        <v>0.7947536843642579</v>
+        <v>0.8052514649746144</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.213832836939056</v>
+        <v>3.119308341734966</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07961869358987297</v>
+        <v>0.07962587973339473</v>
       </c>
       <c r="C36">
-        <v>576.2428327216567</v>
+        <v>567.4040998336063</v>
       </c>
       <c r="D36">
-        <v>784.4208327216567</v>
+        <v>784.3490998336064</v>
       </c>
       <c r="E36">
-        <v>282.078</v>
+        <v>290.845</v>
       </c>
       <c r="F36">
-        <v>298.078</v>
+        <v>306.845</v>
       </c>
       <c r="G36">
         <v>89.90000000000001</v>
@@ -4239,28 +4239,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M36">
-        <v>19.1067998</v>
+        <v>19.6687645</v>
       </c>
       <c r="N36">
-        <v>40.49320019999999</v>
+        <v>39.93123549999999</v>
       </c>
       <c r="O36">
-        <v>7.288776035999998</v>
+        <v>7.187622389999999</v>
       </c>
       <c r="P36">
-        <v>33.20442416399999</v>
+        <v>32.74361310999999</v>
       </c>
       <c r="Q36">
-        <v>65.20442416399999</v>
+        <v>64.74361310999998</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09355699028768633</v>
+        <v>0.09419873805137652</v>
       </c>
       <c r="T36">
-        <v>0.8052514649746144</v>
+        <v>0.8160722542191359</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.119308341734966</v>
+        <v>3.030185246256825</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07962587973339473</v>
+        <v>0.0819356258769165</v>
       </c>
       <c r="C37">
-        <v>567.4040998336063</v>
+        <v>536.2413331515237</v>
       </c>
       <c r="D37">
-        <v>784.3490998336064</v>
+        <v>761.9533331515238</v>
       </c>
       <c r="E37">
-        <v>290.845</v>
+        <v>299.6120000000001</v>
       </c>
       <c r="F37">
-        <v>306.845</v>
+        <v>315.6120000000001</v>
       </c>
       <c r="G37">
         <v>89.90000000000001</v>
@@ -4321,45 +4321,45 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M37">
-        <v>19.6687645</v>
+        <v>22.69250280000001</v>
       </c>
       <c r="N37">
-        <v>39.93123549999999</v>
+        <v>36.90749719999999</v>
       </c>
       <c r="O37">
-        <v>7.187622389999999</v>
+        <v>6.643349495999997</v>
       </c>
       <c r="P37">
-        <v>32.74361310999999</v>
+        <v>30.26414770399999</v>
       </c>
       <c r="Q37">
-        <v>64.74361310999998</v>
+        <v>62.26414770399999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09419873805137652</v>
+        <v>0.09486054043268204</v>
       </c>
       <c r="T37">
-        <v>0.8160722542191359</v>
+        <v>0.8272311931275486</v>
       </c>
       <c r="U37">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V37">
         <v>0.18</v>
       </c>
       <c r="W37">
-        <v>0.052562</v>
+        <v>0.05895800000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.030185246256825</v>
+        <v>2.626418096112341</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0819356258769165</v>
+        <v>0.08200677202043827</v>
       </c>
       <c r="C38">
-        <v>536.2413331515238</v>
+        <v>526.8047720462395</v>
       </c>
       <c r="D38">
-        <v>761.9533331515238</v>
+        <v>761.2837720462395</v>
       </c>
       <c r="E38">
-        <v>299.612</v>
+        <v>308.379</v>
       </c>
       <c r="F38">
-        <v>315.612</v>
+        <v>324.379</v>
       </c>
       <c r="G38">
         <v>89.90000000000001</v>
@@ -4403,28 +4403,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M38">
-        <v>22.6925028</v>
+        <v>23.3228501</v>
       </c>
       <c r="N38">
-        <v>36.90749719999999</v>
+        <v>36.27714989999999</v>
       </c>
       <c r="O38">
-        <v>6.643349495999999</v>
+        <v>6.529886981999998</v>
       </c>
       <c r="P38">
-        <v>30.264147704</v>
+        <v>29.74726291799999</v>
       </c>
       <c r="Q38">
-        <v>62.264147704</v>
+        <v>61.74726291799999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09486054043268204</v>
+        <v>0.09554335241339407</v>
       </c>
       <c r="T38">
-        <v>0.8272311931275486</v>
+        <v>0.8387443840647996</v>
       </c>
       <c r="U38">
         <v>0.07190000000000001</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.626418096112342</v>
+        <v>2.55543382324444</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08200677202043827</v>
+        <v>0.08329315816396003</v>
       </c>
       <c r="C39">
-        <v>526.8047720462395</v>
+        <v>506.131319690627</v>
       </c>
       <c r="D39">
-        <v>761.2837720462395</v>
+        <v>749.377319690627</v>
       </c>
       <c r="E39">
-        <v>308.379</v>
+        <v>317.146</v>
       </c>
       <c r="F39">
-        <v>324.379</v>
+        <v>333.146</v>
       </c>
       <c r="G39">
         <v>89.90000000000001</v>
@@ -4485,45 +4485,45 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M39">
-        <v>23.3228501</v>
+        <v>25.2524668</v>
       </c>
       <c r="N39">
-        <v>36.27714989999999</v>
+        <v>34.34753319999999</v>
       </c>
       <c r="O39">
-        <v>6.529886981999998</v>
+        <v>6.182555975999997</v>
       </c>
       <c r="P39">
-        <v>29.74726291799999</v>
+        <v>28.16497722399999</v>
       </c>
       <c r="Q39">
-        <v>61.74726291799999</v>
+        <v>60.16497722399999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09554335241339407</v>
+        <v>0.0962481905870323</v>
       </c>
       <c r="T39">
-        <v>0.8387443840647996</v>
+        <v>0.8506289682580912</v>
       </c>
       <c r="U39">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V39">
         <v>0.18</v>
       </c>
       <c r="W39">
-        <v>0.05895800000000001</v>
+        <v>0.06215600000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.55543382324444</v>
+        <v>2.3601654631222</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08329315816396003</v>
+        <v>0.08339628430748178</v>
       </c>
       <c r="C40">
-        <v>506.131319690627</v>
+        <v>496.4259162501196</v>
       </c>
       <c r="D40">
-        <v>749.377319690627</v>
+        <v>748.4389162501196</v>
       </c>
       <c r="E40">
-        <v>317.146</v>
+        <v>325.913</v>
       </c>
       <c r="F40">
-        <v>333.146</v>
+        <v>341.913</v>
       </c>
       <c r="G40">
         <v>89.90000000000001</v>
@@ -4567,28 +4567,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M40">
-        <v>25.2524668</v>
+        <v>25.9170054</v>
       </c>
       <c r="N40">
-        <v>34.34753319999999</v>
+        <v>33.68299459999999</v>
       </c>
       <c r="O40">
-        <v>6.182555975999997</v>
+        <v>6.062939027999997</v>
       </c>
       <c r="P40">
-        <v>28.16497722399999</v>
+        <v>27.62005557199999</v>
       </c>
       <c r="Q40">
-        <v>60.16497722399999</v>
+        <v>59.62005557199999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.0962481905870323</v>
+        <v>0.09697613820898653</v>
       </c>
       <c r="T40">
-        <v>0.8506289682580912</v>
+        <v>0.8629032109495234</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.3601654631222</v>
+        <v>2.29964839996522</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08339628430748178</v>
+        <v>0.08349941045100355</v>
       </c>
       <c r="C41">
-        <v>496.4259162501196</v>
+        <v>486.7228600908697</v>
       </c>
       <c r="D41">
-        <v>748.4389162501196</v>
+        <v>747.5028600908698</v>
       </c>
       <c r="E41">
-        <v>325.913</v>
+        <v>334.6800000000001</v>
       </c>
       <c r="F41">
-        <v>341.913</v>
+        <v>350.6800000000001</v>
       </c>
       <c r="G41">
         <v>89.90000000000001</v>
@@ -4649,28 +4649,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M41">
-        <v>25.9170054</v>
+        <v>26.58154400000001</v>
       </c>
       <c r="N41">
-        <v>33.68299459999999</v>
+        <v>33.01845599999999</v>
       </c>
       <c r="O41">
-        <v>6.062939027999997</v>
+        <v>5.943322079999997</v>
       </c>
       <c r="P41">
-        <v>27.62005557199999</v>
+        <v>27.07513391999999</v>
       </c>
       <c r="Q41">
-        <v>59.62005557199999</v>
+        <v>59.07513391999998</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09697613820898653</v>
+        <v>0.09772835075167258</v>
       </c>
       <c r="T41">
-        <v>0.8629032109495234</v>
+        <v>0.8755865950640035</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.29964839996522</v>
+        <v>2.24215718996609</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08349941045100355</v>
+        <v>0.0836025365945253</v>
       </c>
       <c r="C42">
-        <v>486.7228600908697</v>
+        <v>477.0221424167992</v>
       </c>
       <c r="D42">
-        <v>747.5028600908698</v>
+        <v>746.5691424167993</v>
       </c>
       <c r="E42">
-        <v>334.6800000000001</v>
+        <v>343.4470000000001</v>
       </c>
       <c r="F42">
-        <v>350.6800000000001</v>
+        <v>359.4470000000001</v>
       </c>
       <c r="G42">
         <v>89.90000000000001</v>
@@ -4731,28 +4731,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M42">
-        <v>26.58154400000001</v>
+        <v>27.24608260000001</v>
       </c>
       <c r="N42">
-        <v>33.01845599999999</v>
+        <v>32.35391739999999</v>
       </c>
       <c r="O42">
-        <v>5.943322079999997</v>
+        <v>5.823705131999997</v>
       </c>
       <c r="P42">
-        <v>27.07513391999999</v>
+        <v>26.53021226799999</v>
       </c>
       <c r="Q42">
-        <v>59.07513391999998</v>
+        <v>58.53021226799999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09772835075167258</v>
+        <v>0.09850606202461915</v>
       </c>
       <c r="T42">
-        <v>0.8755865950640035</v>
+        <v>0.888699924402703</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.24215718996609</v>
+        <v>2.187470429235209</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0836025365945253</v>
+        <v>0.08370566273804708</v>
       </c>
       <c r="C43">
-        <v>477.0221424167992</v>
+        <v>467.3237544757231</v>
       </c>
       <c r="D43">
-        <v>746.5691424167993</v>
+        <v>745.6377544757232</v>
       </c>
       <c r="E43">
-        <v>343.4470000000001</v>
+        <v>352.2140000000001</v>
       </c>
       <c r="F43">
-        <v>359.4470000000001</v>
+        <v>368.2140000000001</v>
       </c>
       <c r="G43">
         <v>89.90000000000001</v>
@@ -4813,28 +4813,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M43">
-        <v>27.24608260000001</v>
+        <v>27.9106212</v>
       </c>
       <c r="N43">
-        <v>32.35391739999999</v>
+        <v>31.68937879999999</v>
       </c>
       <c r="O43">
-        <v>5.823705131999997</v>
+        <v>5.704088183999998</v>
       </c>
       <c r="P43">
-        <v>26.53021226799999</v>
+        <v>25.98529061599999</v>
       </c>
       <c r="Q43">
-        <v>58.53021226799999</v>
+        <v>57.98529061599999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09850606202461915</v>
+        <v>0.09931059092766736</v>
       </c>
       <c r="T43">
-        <v>0.888699924402703</v>
+        <v>0.9022654375117027</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.187470429235209</v>
+        <v>2.135387799967705</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08370566273804708</v>
+        <v>0.08380878888156883</v>
       </c>
       <c r="C44">
-        <v>467.3237544757232</v>
+        <v>457.627687559079</v>
       </c>
       <c r="D44">
-        <v>745.6377544757232</v>
+        <v>744.7086875590791</v>
       </c>
       <c r="E44">
-        <v>352.214</v>
+        <v>360.981</v>
       </c>
       <c r="F44">
-        <v>368.214</v>
+        <v>376.981</v>
       </c>
       <c r="G44">
         <v>89.90000000000001</v>
@@ -4895,28 +4895,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M44">
-        <v>27.9106212</v>
+        <v>28.5751598</v>
       </c>
       <c r="N44">
-        <v>31.68937879999999</v>
+        <v>31.02484019999999</v>
       </c>
       <c r="O44">
-        <v>5.704088183999999</v>
+        <v>5.584471235999999</v>
       </c>
       <c r="P44">
-        <v>25.98529061599999</v>
+        <v>25.44036896399999</v>
       </c>
       <c r="Q44">
-        <v>57.98529061599999</v>
+        <v>57.44036896399999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09931059092766736</v>
+        <v>0.100143348915033</v>
       </c>
       <c r="T44">
-        <v>0.9022654375117027</v>
+        <v>0.9163069335368075</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.135387799967705</v>
+        <v>2.085727618573107</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08380878888156883</v>
+        <v>0.08391191502509059</v>
       </c>
       <c r="C45">
-        <v>457.627687559079</v>
+        <v>447.9339330016526</v>
       </c>
       <c r="D45">
-        <v>744.7086875590791</v>
+        <v>743.7819330016526</v>
       </c>
       <c r="E45">
-        <v>360.981</v>
+        <v>369.748</v>
       </c>
       <c r="F45">
-        <v>376.981</v>
+        <v>385.748</v>
       </c>
       <c r="G45">
         <v>89.90000000000001</v>
@@ -4977,28 +4977,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M45">
-        <v>28.5751598</v>
+        <v>29.23969840000001</v>
       </c>
       <c r="N45">
-        <v>31.02484019999999</v>
+        <v>30.36030159999999</v>
       </c>
       <c r="O45">
-        <v>5.584471235999999</v>
+        <v>5.464854287999998</v>
       </c>
       <c r="P45">
-        <v>25.44036896399999</v>
+        <v>24.89544731199999</v>
       </c>
       <c r="Q45">
-        <v>57.44036896399999</v>
+        <v>56.89544731199999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.100143348915033</v>
+        <v>0.1010058482590903</v>
       </c>
       <c r="T45">
-        <v>0.9163069335368075</v>
+        <v>0.9308499115628091</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.085727618573107</v>
+        <v>2.038324718150991</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08391191502509059</v>
+        <v>0.08925484116861235</v>
       </c>
       <c r="C46">
-        <v>447.9339330016526</v>
+        <v>394.1164944812331</v>
       </c>
       <c r="D46">
-        <v>743.7819330016526</v>
+        <v>698.7314944812332</v>
       </c>
       <c r="E46">
-        <v>369.748</v>
+        <v>378.515</v>
       </c>
       <c r="F46">
-        <v>385.748</v>
+        <v>394.515</v>
       </c>
       <c r="G46">
         <v>89.90000000000001</v>
@@ -5059,45 +5059,45 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M46">
-        <v>29.23969840000001</v>
+        <v>35.50635</v>
       </c>
       <c r="N46">
-        <v>30.36030159999999</v>
+        <v>24.09364999999999</v>
       </c>
       <c r="O46">
-        <v>5.464854287999998</v>
+        <v>4.336856999999998</v>
       </c>
       <c r="P46">
-        <v>24.89544731199999</v>
+        <v>19.75679299999999</v>
       </c>
       <c r="Q46">
-        <v>56.89544731199999</v>
+        <v>51.75679299999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1010058482590903</v>
+        <v>0.1018997112156588</v>
       </c>
       <c r="T46">
-        <v>0.9308499115628091</v>
+        <v>0.9459217251533923</v>
       </c>
       <c r="U46">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V46">
         <v>0.18</v>
       </c>
       <c r="W46">
-        <v>0.06215600000000001</v>
+        <v>0.0738</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.038324718150991</v>
+        <v>1.678572987648688</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08925484116861235</v>
+        <v>0.0894744073121341</v>
       </c>
       <c r="C47">
-        <v>394.1164944812331</v>
+        <v>383.6146111770787</v>
       </c>
       <c r="D47">
-        <v>698.7314944812332</v>
+        <v>696.9966111770788</v>
       </c>
       <c r="E47">
-        <v>378.515</v>
+        <v>387.282</v>
       </c>
       <c r="F47">
-        <v>394.515</v>
+        <v>403.282</v>
       </c>
       <c r="G47">
         <v>89.90000000000001</v>
@@ -5141,28 +5141,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M47">
-        <v>35.50635</v>
+        <v>36.29538</v>
       </c>
       <c r="N47">
-        <v>24.09364999999999</v>
+        <v>23.30461999999999</v>
       </c>
       <c r="O47">
-        <v>4.336856999999998</v>
+        <v>4.194831599999999</v>
       </c>
       <c r="P47">
-        <v>19.75679299999999</v>
+        <v>19.10978839999999</v>
       </c>
       <c r="Q47">
-        <v>51.75679299999999</v>
+        <v>51.10978839999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1018997112156588</v>
+        <v>0.1028266802076557</v>
       </c>
       <c r="T47">
-        <v>0.9459217251533923</v>
+        <v>0.9615517540621454</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.678572987648688</v>
+        <v>1.64208227052589</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0894744073121341</v>
+        <v>0.08969397345565587</v>
       </c>
       <c r="C48">
-        <v>383.6146111770787</v>
+        <v>373.1213216332373</v>
       </c>
       <c r="D48">
-        <v>696.9966111770788</v>
+        <v>695.2703216332374</v>
       </c>
       <c r="E48">
-        <v>387.282</v>
+        <v>396.049</v>
       </c>
       <c r="F48">
-        <v>403.282</v>
+        <v>412.049</v>
       </c>
       <c r="G48">
         <v>89.90000000000001</v>
@@ -5223,28 +5223,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M48">
-        <v>36.29538</v>
+        <v>37.08441</v>
       </c>
       <c r="N48">
-        <v>23.30461999999999</v>
+        <v>22.51559</v>
       </c>
       <c r="O48">
-        <v>4.194831599999999</v>
+        <v>4.052806199999999</v>
       </c>
       <c r="P48">
-        <v>19.10978839999999</v>
+        <v>18.4627838</v>
       </c>
       <c r="Q48">
-        <v>51.10978839999999</v>
+        <v>50.4627838</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1028266802076557</v>
+        <v>0.1037886291616148</v>
       </c>
       <c r="T48">
-        <v>0.9615517540621454</v>
+        <v>0.9777715953825497</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.64208227052589</v>
+        <v>1.607144349876404</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08969397345565587</v>
+        <v>0.08991353959917764</v>
       </c>
       <c r="C49">
-        <v>373.1213216332373</v>
+        <v>362.6365621535631</v>
       </c>
       <c r="D49">
-        <v>695.2703216332374</v>
+        <v>693.5525621535631</v>
       </c>
       <c r="E49">
-        <v>396.049</v>
+        <v>404.816</v>
       </c>
       <c r="F49">
-        <v>412.049</v>
+        <v>420.816</v>
       </c>
       <c r="G49">
         <v>89.90000000000001</v>
@@ -5305,28 +5305,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M49">
-        <v>37.08441</v>
+        <v>37.87344</v>
       </c>
       <c r="N49">
-        <v>22.51559</v>
+        <v>21.72655999999999</v>
       </c>
       <c r="O49">
-        <v>4.052806199999999</v>
+        <v>3.910780799999999</v>
       </c>
       <c r="P49">
-        <v>18.4627838</v>
+        <v>17.81577919999999</v>
       </c>
       <c r="Q49">
-        <v>50.4627838</v>
+        <v>49.81577919999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1037886291616148</v>
+        <v>0.1047875761522647</v>
       </c>
       <c r="T49">
-        <v>0.9777715953825497</v>
+        <v>0.9946152767537386</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.607144349876404</v>
+        <v>1.573662175920645</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08991353959917764</v>
+        <v>0.09013310574269939</v>
       </c>
       <c r="C50">
-        <v>362.6365621535631</v>
+        <v>352.1602696698392</v>
       </c>
       <c r="D50">
-        <v>693.5525621535631</v>
+        <v>691.8432696698393</v>
       </c>
       <c r="E50">
-        <v>404.816</v>
+        <v>413.583</v>
       </c>
       <c r="F50">
-        <v>420.816</v>
+        <v>429.583</v>
       </c>
       <c r="G50">
         <v>89.90000000000001</v>
@@ -5387,28 +5387,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M50">
-        <v>37.87344</v>
+        <v>38.66247</v>
       </c>
       <c r="N50">
-        <v>21.72655999999999</v>
+        <v>20.93753</v>
       </c>
       <c r="O50">
-        <v>3.910780799999999</v>
+        <v>3.768755399999999</v>
       </c>
       <c r="P50">
-        <v>17.81577919999999</v>
+        <v>17.1687746</v>
       </c>
       <c r="Q50">
-        <v>49.81577919999999</v>
+        <v>49.16877459999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1047875761522647</v>
+        <v>0.1058256975347047</v>
       </c>
       <c r="T50">
-        <v>0.9946152767537385</v>
+        <v>1.012119494649288</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.573662175920645</v>
+        <v>1.54154662131002</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09013310574269939</v>
+        <v>0.09035267188622115</v>
       </c>
       <c r="C51">
-        <v>352.1602696698392</v>
+        <v>341.6923817340577</v>
       </c>
       <c r="D51">
-        <v>691.8432696698393</v>
+        <v>690.1423817340577</v>
       </c>
       <c r="E51">
-        <v>413.583</v>
+        <v>422.35</v>
       </c>
       <c r="F51">
-        <v>429.583</v>
+        <v>438.35</v>
       </c>
       <c r="G51">
         <v>89.90000000000001</v>
@@ -5469,28 +5469,28 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M51">
-        <v>38.66247</v>
+        <v>39.4515</v>
       </c>
       <c r="N51">
-        <v>20.93753</v>
+        <v>20.14849999999999</v>
       </c>
       <c r="O51">
-        <v>3.768755399999999</v>
+        <v>3.626729999999998</v>
       </c>
       <c r="P51">
-        <v>17.1687746</v>
+        <v>16.52176999999999</v>
       </c>
       <c r="Q51">
-        <v>49.16877459999999</v>
+        <v>48.52176999999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1058256975347047</v>
+        <v>0.1069053437724423</v>
       </c>
       <c r="T51">
-        <v>1.012119494649288</v>
+        <v>1.030323881260659</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.54154662131002</v>
+        <v>1.510715688883819</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09035267188622115</v>
+        <v>0.1158489117170514</v>
       </c>
       <c r="C52">
-        <v>341.6923817340577</v>
+        <v>179.6574001900637</v>
       </c>
       <c r="D52">
-        <v>690.1423817340577</v>
+        <v>536.8744001900637</v>
       </c>
       <c r="E52">
-        <v>422.35</v>
+        <v>431.117</v>
       </c>
       <c r="F52">
-        <v>438.35</v>
+        <v>447.117</v>
       </c>
       <c r="G52">
         <v>89.90000000000001</v>
@@ -5551,45 +5551,45 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M52">
-        <v>39.4515</v>
+        <v>65.63677560000001</v>
       </c>
       <c r="N52">
-        <v>20.14849999999999</v>
+        <v>-6.036775600000013</v>
       </c>
       <c r="O52">
-        <v>3.626729999999998</v>
+        <v>-1.086619608000002</v>
       </c>
       <c r="P52">
-        <v>16.52176999999999</v>
+        <v>-4.950155992000011</v>
       </c>
       <c r="Q52">
-        <v>48.52176999999999</v>
+        <v>27.04984400799999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1069053437724423</v>
+        <v>0.1086075689734904</v>
       </c>
       <c r="T52">
-        <v>1.030323881260659</v>
+        <v>1.059025843603837</v>
       </c>
       <c r="U52">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.18</v>
+        <v>0.1634449575246959</v>
       </c>
       <c r="W52">
-        <v>0.0738</v>
+        <v>0.1228062802353747</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y52">
-        <v>1.510715688883819</v>
+        <v>0.9080275418038662</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1158489117170514</v>
+        <v>0.1168589117170514</v>
       </c>
       <c r="C53">
-        <v>179.6574001900637</v>
+        <v>166.2084510915391</v>
       </c>
       <c r="D53">
-        <v>536.8744001900637</v>
+        <v>532.1924510915392</v>
       </c>
       <c r="E53">
-        <v>431.117</v>
+        <v>439.884</v>
       </c>
       <c r="F53">
-        <v>447.117</v>
+        <v>455.884</v>
       </c>
       <c r="G53">
         <v>89.90000000000001</v>
@@ -5633,37 +5633,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M53">
-        <v>65.63677560000001</v>
+        <v>66.9237712</v>
       </c>
       <c r="N53">
-        <v>-6.036775600000013</v>
+        <v>-7.32377120000001</v>
       </c>
       <c r="O53">
-        <v>-1.086619608000002</v>
+        <v>-1.318278816000002</v>
       </c>
       <c r="P53">
-        <v>-4.950155992000011</v>
+        <v>-6.005492384000008</v>
       </c>
       <c r="Q53">
-        <v>27.04984400799999</v>
+        <v>25.99450761599999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1086075689734904</v>
+        <v>0.1099160599937714</v>
       </c>
       <c r="T53">
-        <v>1.059025843603837</v>
+        <v>1.08108888201225</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.1634449575246959</v>
+        <v>0.1603017852646056</v>
       </c>
       <c r="W53">
-        <v>0.1228062802353747</v>
+        <v>0.1232676979231559</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.9080275418038662</v>
+        <v>0.8905654736922535</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1168589117170514</v>
+        <v>0.1178689117170514</v>
       </c>
       <c r="C54">
-        <v>166.2084510915391</v>
+        <v>152.8404562552627</v>
       </c>
       <c r="D54">
-        <v>532.1924510915392</v>
+        <v>527.5914562552628</v>
       </c>
       <c r="E54">
-        <v>439.884</v>
+        <v>448.6510000000001</v>
       </c>
       <c r="F54">
-        <v>455.884</v>
+        <v>464.6510000000001</v>
       </c>
       <c r="G54">
         <v>89.90000000000001</v>
@@ -5715,37 +5715,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M54">
-        <v>66.9237712</v>
+        <v>68.21076680000002</v>
       </c>
       <c r="N54">
-        <v>-7.32377120000001</v>
+        <v>-8.610766800000022</v>
       </c>
       <c r="O54">
-        <v>-1.318278816000002</v>
+        <v>-1.549938024000004</v>
       </c>
       <c r="P54">
-        <v>-6.005492384000008</v>
+        <v>-7.060828776000018</v>
       </c>
       <c r="Q54">
-        <v>25.99450761599999</v>
+        <v>24.93917122399998</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1099160599937714</v>
+        <v>0.1112802314830006</v>
       </c>
       <c r="T54">
-        <v>1.08108888201225</v>
+        <v>1.104090773118894</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.1603017852646056</v>
+        <v>0.157277223278481</v>
       </c>
       <c r="W54">
-        <v>0.1232676979231559</v>
+        <v>0.123711703622719</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8905654736922535</v>
+        <v>0.8737623515471165</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1178689117170514</v>
+        <v>0.1188789117170514</v>
       </c>
       <c r="C55">
-        <v>152.8404562552627</v>
+        <v>139.5513340417577</v>
       </c>
       <c r="D55">
-        <v>527.5914562552628</v>
+        <v>523.0693340417578</v>
       </c>
       <c r="E55">
-        <v>448.6510000000001</v>
+        <v>457.4180000000001</v>
       </c>
       <c r="F55">
-        <v>464.6510000000001</v>
+        <v>473.4180000000001</v>
       </c>
       <c r="G55">
         <v>89.90000000000001</v>
@@ -5797,37 +5797,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M55">
-        <v>68.21076680000002</v>
+        <v>69.49776240000001</v>
       </c>
       <c r="N55">
-        <v>-8.610766800000022</v>
+        <v>-9.897762400000019</v>
       </c>
       <c r="O55">
-        <v>-1.549938024000004</v>
+        <v>-1.781597232000003</v>
       </c>
       <c r="P55">
-        <v>-7.060828776000018</v>
+        <v>-8.116165168000016</v>
       </c>
       <c r="Q55">
-        <v>24.93917122399998</v>
+        <v>23.88383483199998</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1112802314830006</v>
+        <v>0.1127037147761093</v>
       </c>
       <c r="T55">
-        <v>1.104090773118894</v>
+        <v>1.128092746447565</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.157277223278481</v>
+        <v>0.1543646821066572</v>
       </c>
       <c r="W55">
-        <v>0.123711703622719</v>
+        <v>0.1241392646667427</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8737623515471165</v>
+        <v>0.8575815672592069</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1188789117170514</v>
+        <v>0.1198889117170514</v>
       </c>
       <c r="C56">
-        <v>139.5513340417577</v>
+        <v>126.3390735740954</v>
       </c>
       <c r="D56">
-        <v>523.0693340417578</v>
+        <v>518.6240735740955</v>
       </c>
       <c r="E56">
-        <v>457.4180000000001</v>
+        <v>466.1850000000001</v>
       </c>
       <c r="F56">
-        <v>473.4180000000001</v>
+        <v>482.1850000000001</v>
       </c>
       <c r="G56">
         <v>89.90000000000001</v>
@@ -5879,37 +5879,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M56">
-        <v>69.49776240000001</v>
+        <v>70.78475800000001</v>
       </c>
       <c r="N56">
-        <v>-9.897762400000019</v>
+        <v>-11.18475800000002</v>
       </c>
       <c r="O56">
-        <v>-1.781597232000003</v>
+        <v>-2.013256440000003</v>
       </c>
       <c r="P56">
-        <v>-8.116165168000016</v>
+        <v>-9.171501560000014</v>
       </c>
       <c r="Q56">
-        <v>23.88383483199998</v>
+        <v>22.82849843999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1127037147761093</v>
+        <v>0.1141904639933562</v>
       </c>
       <c r="T56">
-        <v>1.128092746447565</v>
+        <v>1.1531614741464</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.1543646821066572</v>
+        <v>0.1515580515228998</v>
       </c>
       <c r="W56">
-        <v>0.1241392646667427</v>
+        <v>0.1245512780364383</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8575815672592069</v>
+        <v>0.8419891751272214</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1198889117170514</v>
+        <v>0.1208989117170514</v>
       </c>
       <c r="C57">
-        <v>126.3390735740954</v>
+        <v>113.2017317563853</v>
       </c>
       <c r="D57">
-        <v>518.6240735740955</v>
+        <v>514.2537317563854</v>
       </c>
       <c r="E57">
-        <v>466.1850000000001</v>
+        <v>474.9520000000001</v>
       </c>
       <c r="F57">
-        <v>482.1850000000001</v>
+        <v>490.9520000000001</v>
       </c>
       <c r="G57">
         <v>89.90000000000001</v>
@@ -5961,37 +5961,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M57">
-        <v>70.78475800000001</v>
+        <v>72.07175360000001</v>
       </c>
       <c r="N57">
-        <v>-11.18475800000002</v>
+        <v>-12.47175360000001</v>
       </c>
       <c r="O57">
-        <v>-2.013256440000003</v>
+        <v>-2.244915648000002</v>
       </c>
       <c r="P57">
-        <v>-9.171501560000014</v>
+        <v>-10.22683795200001</v>
       </c>
       <c r="Q57">
-        <v>22.82849843999999</v>
+        <v>21.77316204799999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1141904639933562</v>
+        <v>0.1157447927204779</v>
       </c>
       <c r="T57">
-        <v>1.1531614741464</v>
+        <v>1.179369689467909</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.1515580515228998</v>
+        <v>0.1488516577457052</v>
       </c>
       <c r="W57">
-        <v>0.1245512780364383</v>
+        <v>0.1249485766429305</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8419891751272214</v>
+        <v>0.8269536541428067</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1208989117170514</v>
+        <v>0.1219089117170514</v>
       </c>
       <c r="C58">
-        <v>113.2017317563853</v>
+        <v>100.1374304417533</v>
       </c>
       <c r="D58">
-        <v>514.2537317563854</v>
+        <v>509.9564304417534</v>
       </c>
       <c r="E58">
-        <v>474.9520000000001</v>
+        <v>483.7190000000001</v>
       </c>
       <c r="F58">
-        <v>490.9520000000001</v>
+        <v>499.7190000000001</v>
       </c>
       <c r="G58">
         <v>89.90000000000001</v>
@@ -6043,37 +6043,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M58">
-        <v>72.07175360000001</v>
+        <v>73.35874920000002</v>
       </c>
       <c r="N58">
-        <v>-12.47175360000001</v>
+        <v>-13.75874920000003</v>
       </c>
       <c r="O58">
-        <v>-2.244915648000002</v>
+        <v>-2.476574856000004</v>
       </c>
       <c r="P58">
-        <v>-10.22683795200001</v>
+        <v>-11.28217434400002</v>
       </c>
       <c r="Q58">
-        <v>21.77316204799999</v>
+        <v>20.71782565599998</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1157447927204779</v>
+        <v>0.1173714158070007</v>
       </c>
       <c r="T58">
-        <v>1.179369689467909</v>
+        <v>1.206796891548559</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1488516577457052</v>
+        <v>0.1462402251536753</v>
       </c>
       <c r="W58">
-        <v>0.1249485766429305</v>
+        <v>0.1253319349474405</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8269536541428067</v>
+        <v>0.812445695298196</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1219089117170514</v>
+        <v>0.1549915383072338</v>
       </c>
       <c r="C59">
-        <v>100.1374304417533</v>
+        <v>-18.21633890665726</v>
       </c>
       <c r="D59">
-        <v>509.9564304417534</v>
+        <v>400.3696610933428</v>
       </c>
       <c r="E59">
-        <v>483.7190000000001</v>
+        <v>492.4860000000001</v>
       </c>
       <c r="F59">
-        <v>499.7190000000001</v>
+        <v>508.4860000000001</v>
       </c>
       <c r="G59">
         <v>89.90000000000001</v>
@@ -6125,45 +6125,45 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M59">
-        <v>73.35874920000002</v>
+        <v>102.1039888</v>
       </c>
       <c r="N59">
-        <v>-13.75874920000003</v>
+        <v>-42.50398880000003</v>
       </c>
       <c r="O59">
-        <v>-2.476574856000004</v>
+        <v>-7.650717984000005</v>
       </c>
       <c r="P59">
-        <v>-11.28217434400002</v>
+        <v>-34.85327081600003</v>
       </c>
       <c r="Q59">
-        <v>20.71782565599998</v>
+        <v>-2.853270816000027</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1173714158070007</v>
+        <v>0.1208674652076017</v>
       </c>
       <c r="T59">
-        <v>1.206796891548559</v>
+        <v>1.265745306942807</v>
       </c>
       <c r="U59">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1462402251536753</v>
+        <v>0.1050693525892888</v>
       </c>
       <c r="W59">
-        <v>0.1253319349474405</v>
+        <v>0.1797020740000708</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.812445695298196</v>
+        <v>0.5837186254960489</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1549915383072338</v>
+        <v>0.1565415383072338</v>
       </c>
       <c r="C60">
-        <v>-18.21633890665714</v>
+        <v>-30.97420521551715</v>
       </c>
       <c r="D60">
-        <v>400.3696610933428</v>
+        <v>396.3787947844829</v>
       </c>
       <c r="E60">
-        <v>492.486</v>
+        <v>501.253</v>
       </c>
       <c r="F60">
-        <v>508.486</v>
+        <v>517.253</v>
       </c>
       <c r="G60">
         <v>89.90000000000001</v>
@@ -6207,37 +6207,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M60">
-        <v>102.1039888</v>
+        <v>103.8644024</v>
       </c>
       <c r="N60">
-        <v>-42.5039888</v>
+        <v>-44.26440240000002</v>
       </c>
       <c r="O60">
-        <v>-7.650717984</v>
+        <v>-7.967592432000004</v>
       </c>
       <c r="P60">
-        <v>-34.85327081600001</v>
+        <v>-36.29680996800002</v>
       </c>
       <c r="Q60">
-        <v>-2.853270816000006</v>
+        <v>-4.296809968000019</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1208674652076017</v>
+        <v>0.122698378993153</v>
       </c>
       <c r="T60">
-        <v>1.265745306942807</v>
+        <v>1.296617143697509</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1050693525892888</v>
+        <v>0.1032885161047246</v>
       </c>
       <c r="W60">
-        <v>0.1797020740000708</v>
+        <v>0.1800596659661713</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5837186254960491</v>
+        <v>0.5738250894706922</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1565415383072338</v>
+        <v>0.1580915383072338</v>
       </c>
       <c r="C61">
-        <v>-30.97420521551715</v>
+        <v>-43.65329522048035</v>
       </c>
       <c r="D61">
-        <v>396.3787947844829</v>
+        <v>392.4667047795197</v>
       </c>
       <c r="E61">
-        <v>501.253</v>
+        <v>510.02</v>
       </c>
       <c r="F61">
-        <v>517.253</v>
+        <v>526.02</v>
       </c>
       <c r="G61">
         <v>89.90000000000001</v>
@@ -6289,37 +6289,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M61">
-        <v>103.8644024</v>
+        <v>105.624816</v>
       </c>
       <c r="N61">
-        <v>-44.26440240000002</v>
+        <v>-46.024816</v>
       </c>
       <c r="O61">
-        <v>-7.967592432000004</v>
+        <v>-8.28446688</v>
       </c>
       <c r="P61">
-        <v>-36.29680996800002</v>
+        <v>-37.74034912</v>
       </c>
       <c r="Q61">
-        <v>-4.296809968000019</v>
+        <v>-5.740349120000005</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.122698378993153</v>
+        <v>0.1246208384679818</v>
       </c>
       <c r="T61">
-        <v>1.296617143697509</v>
+        <v>1.329032572289947</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1032885161047246</v>
+        <v>0.1015670408363125</v>
       </c>
       <c r="W61">
-        <v>0.1800596659661713</v>
+        <v>0.1804053382000685</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5738250894706922</v>
+        <v>0.5642613379795142</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1580915383072338</v>
+        <v>0.1596415383072338</v>
       </c>
       <c r="C62">
-        <v>-43.65329522048035</v>
+        <v>-56.25591859186056</v>
       </c>
       <c r="D62">
-        <v>392.4667047795197</v>
+        <v>388.6310814081394</v>
       </c>
       <c r="E62">
-        <v>510.02</v>
+        <v>518.787</v>
       </c>
       <c r="F62">
-        <v>526.02</v>
+        <v>534.787</v>
       </c>
       <c r="G62">
         <v>89.90000000000001</v>
@@ -6371,37 +6371,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M62">
-        <v>105.624816</v>
+        <v>107.3852296</v>
       </c>
       <c r="N62">
-        <v>-46.024816</v>
+        <v>-47.78522960000002</v>
       </c>
       <c r="O62">
-        <v>-8.28446688</v>
+        <v>-8.601341328000004</v>
       </c>
       <c r="P62">
-        <v>-37.74034912</v>
+        <v>-39.18388827200002</v>
       </c>
       <c r="Q62">
-        <v>-5.740349120000005</v>
+        <v>-7.183888272000019</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1246208384679818</v>
+        <v>0.1266418856081865</v>
       </c>
       <c r="T62">
-        <v>1.329032572289947</v>
+        <v>1.363110330553792</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1015670408363125</v>
+        <v>0.09990200737997955</v>
       </c>
       <c r="W62">
-        <v>0.1804053382000685</v>
+        <v>0.1807396769181001</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5642613379795142</v>
+        <v>0.5550111521109975</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1596415383072338</v>
+        <v>0.1611915383072338</v>
       </c>
       <c r="C63">
-        <v>-56.25591859186056</v>
+        <v>-68.78429558313132</v>
       </c>
       <c r="D63">
-        <v>388.6310814081394</v>
+        <v>384.8697044168687</v>
       </c>
       <c r="E63">
-        <v>518.787</v>
+        <v>527.554</v>
       </c>
       <c r="F63">
-        <v>534.787</v>
+        <v>543.554</v>
       </c>
       <c r="G63">
         <v>89.90000000000001</v>
@@ -6453,37 +6453,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M63">
-        <v>107.3852296</v>
+        <v>109.1456432</v>
       </c>
       <c r="N63">
-        <v>-47.78522960000002</v>
+        <v>-49.5456432</v>
       </c>
       <c r="O63">
-        <v>-8.601341328000004</v>
+        <v>-8.918215776</v>
       </c>
       <c r="P63">
-        <v>-39.18388827200002</v>
+        <v>-40.627427424</v>
       </c>
       <c r="Q63">
-        <v>-7.183888272000019</v>
+        <v>-8.627427424000004</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1266418856081865</v>
+        <v>0.1287693036505071</v>
       </c>
       <c r="T63">
-        <v>1.363110330553792</v>
+        <v>1.39898165504205</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.09990200737997955</v>
+        <v>0.09829068468030246</v>
       </c>
       <c r="W63">
-        <v>0.1807396769181001</v>
+        <v>0.1810632305161953</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5550111521109975</v>
+        <v>0.5460593593350137</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1611915383072338</v>
+        <v>0.1627415383072338</v>
       </c>
       <c r="C64">
-        <v>-68.78429558313132</v>
+        <v>-81.24056131656505</v>
       </c>
       <c r="D64">
-        <v>384.8697044168687</v>
+        <v>381.1804386834349</v>
       </c>
       <c r="E64">
-        <v>527.554</v>
+        <v>536.321</v>
       </c>
       <c r="F64">
-        <v>543.554</v>
+        <v>552.321</v>
       </c>
       <c r="G64">
         <v>89.90000000000001</v>
@@ -6535,37 +6535,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M64">
-        <v>109.1456432</v>
+        <v>110.9060568</v>
       </c>
       <c r="N64">
-        <v>-49.5456432</v>
+        <v>-51.30605680000001</v>
       </c>
       <c r="O64">
-        <v>-8.918215776</v>
+        <v>-9.235090224</v>
       </c>
       <c r="P64">
-        <v>-40.627427424</v>
+        <v>-42.070966576</v>
       </c>
       <c r="Q64">
-        <v>-8.627427424000004</v>
+        <v>-10.070966576</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1287693036505071</v>
+        <v>0.131011717262683</v>
       </c>
       <c r="T64">
-        <v>1.39898165504205</v>
+        <v>1.436791970043186</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.09829068468030246</v>
+        <v>0.09673051508220241</v>
       </c>
       <c r="W64">
-        <v>0.1810632305161953</v>
+        <v>0.1813765125714938</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5460593593350137</v>
+        <v>0.5373917504566801</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1627415383072338</v>
+        <v>0.1642915383072338</v>
       </c>
       <c r="C65">
-        <v>-81.24056131656505</v>
+        <v>-93.62676982472567</v>
       </c>
       <c r="D65">
-        <v>381.1804386834349</v>
+        <v>377.5612301752744</v>
       </c>
       <c r="E65">
-        <v>536.321</v>
+        <v>545.0880000000001</v>
       </c>
       <c r="F65">
-        <v>552.321</v>
+        <v>561.0880000000001</v>
       </c>
       <c r="G65">
         <v>89.90000000000001</v>
@@ -6617,37 +6617,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M65">
-        <v>110.9060568</v>
+        <v>112.6664704</v>
       </c>
       <c r="N65">
-        <v>-51.30605680000001</v>
+        <v>-53.06647040000003</v>
       </c>
       <c r="O65">
-        <v>-9.235090224</v>
+        <v>-9.551964672000004</v>
       </c>
       <c r="P65">
-        <v>-42.070966576</v>
+        <v>-43.51450572800002</v>
       </c>
       <c r="Q65">
-        <v>-10.070966576</v>
+        <v>-11.51450572800002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.131011717262683</v>
+        <v>0.1333787094088687</v>
       </c>
       <c r="T65">
-        <v>1.436791970043186</v>
+        <v>1.476702858099941</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.09673051508220241</v>
+        <v>0.09521910078404298</v>
       </c>
       <c r="W65">
-        <v>0.1813765125714938</v>
+        <v>0.1816800045625642</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5373917504566801</v>
+        <v>0.5289950043557945</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1642915383072338</v>
+        <v>0.1658415383072338</v>
       </c>
       <c r="C66">
-        <v>-93.62676982472567</v>
+        <v>-105.9448978638881</v>
       </c>
       <c r="D66">
-        <v>377.5612301752744</v>
+        <v>374.0101021361119</v>
       </c>
       <c r="E66">
-        <v>545.0880000000001</v>
+        <v>553.855</v>
       </c>
       <c r="F66">
-        <v>561.0880000000001</v>
+        <v>569.855</v>
       </c>
       <c r="G66">
         <v>89.90000000000001</v>
@@ -6699,37 +6699,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M66">
-        <v>112.6664704</v>
+        <v>114.426884</v>
       </c>
       <c r="N66">
-        <v>-53.06647040000003</v>
+        <v>-54.82688400000001</v>
       </c>
       <c r="O66">
-        <v>-9.551964672000004</v>
+        <v>-9.868839120000001</v>
       </c>
       <c r="P66">
-        <v>-43.51450572800002</v>
+        <v>-44.95804488</v>
       </c>
       <c r="Q66">
-        <v>-11.51450572800002</v>
+        <v>-12.95804488</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1333787094088687</v>
+        <v>0.1358809582491221</v>
       </c>
       <c r="T66">
-        <v>1.476702858099941</v>
+        <v>1.518894368331368</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.09521910078404298</v>
+        <v>0.09375419154121158</v>
       </c>
       <c r="W66">
-        <v>0.1816800045625642</v>
+        <v>0.1819741583385247</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5289950043557945</v>
+        <v>0.5208566196733977</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1658415383072338</v>
+        <v>0.1673915383072338</v>
       </c>
       <c r="C67">
-        <v>-105.9448978638881</v>
+        <v>-118.1968485142636</v>
       </c>
       <c r="D67">
-        <v>374.0101021361119</v>
+        <v>370.5251514857364</v>
       </c>
       <c r="E67">
-        <v>553.855</v>
+        <v>562.6220000000001</v>
       </c>
       <c r="F67">
-        <v>569.855</v>
+        <v>578.6220000000001</v>
       </c>
       <c r="G67">
         <v>89.90000000000001</v>
@@ -6781,37 +6781,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M67">
-        <v>114.426884</v>
+        <v>116.1872976</v>
       </c>
       <c r="N67">
-        <v>-54.82688400000001</v>
+        <v>-56.58729760000003</v>
       </c>
       <c r="O67">
-        <v>-9.868839120000001</v>
+        <v>-10.185713568</v>
       </c>
       <c r="P67">
-        <v>-44.95804488</v>
+        <v>-46.40158403200002</v>
       </c>
       <c r="Q67">
-        <v>-12.95804488</v>
+        <v>-14.40158403200002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1358809582491221</v>
+        <v>0.1385303981976257</v>
       </c>
       <c r="T67">
-        <v>1.518894368331368</v>
+        <v>1.56356773210582</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.09375419154121158</v>
+        <v>0.09233367348755683</v>
       </c>
       <c r="W67">
-        <v>0.1819741583385247</v>
+        <v>0.1822593983636986</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5208566196733977</v>
+        <v>0.5129648527086491</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1673915383072338</v>
+        <v>0.1689415383072338</v>
       </c>
       <c r="C68">
-        <v>-118.1968485142636</v>
+        <v>-130.3844545808047</v>
       </c>
       <c r="D68">
-        <v>370.5251514857364</v>
+        <v>367.1045454191953</v>
       </c>
       <c r="E68">
-        <v>562.6220000000001</v>
+        <v>571.389</v>
       </c>
       <c r="F68">
-        <v>578.6220000000001</v>
+        <v>587.389</v>
       </c>
       <c r="G68">
         <v>89.90000000000001</v>
@@ -6863,37 +6863,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M68">
-        <v>116.1872976</v>
+        <v>117.9477112</v>
       </c>
       <c r="N68">
-        <v>-56.58729760000003</v>
+        <v>-58.34771120000001</v>
       </c>
       <c r="O68">
-        <v>-10.185713568</v>
+        <v>-10.502588016</v>
       </c>
       <c r="P68">
-        <v>-46.40158403200002</v>
+        <v>-47.845123184</v>
       </c>
       <c r="Q68">
-        <v>-14.40158403200002</v>
+        <v>-15.845123184</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1385303981976257</v>
+        <v>0.1413404102642204</v>
       </c>
       <c r="T68">
-        <v>1.56356773210582</v>
+        <v>1.610948572472663</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.09233367348755683</v>
+        <v>0.09095555895789183</v>
       </c>
       <c r="W68">
-        <v>0.1822593983636986</v>
+        <v>0.1825361237612553</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5129648527086491</v>
+        <v>0.5053086608771769</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1689415383072338</v>
+        <v>0.1945952322270935</v>
       </c>
       <c r="C69">
-        <v>-130.3844545808047</v>
+        <v>-187.8080809845276</v>
       </c>
       <c r="D69">
-        <v>367.1045454191953</v>
+        <v>318.4479190154725</v>
       </c>
       <c r="E69">
-        <v>571.389</v>
+        <v>580.1560000000001</v>
       </c>
       <c r="F69">
-        <v>587.389</v>
+        <v>596.1560000000001</v>
       </c>
       <c r="G69">
         <v>89.90000000000001</v>
@@ -6945,45 +6945,45 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M69">
-        <v>117.9477112</v>
+        <v>140.5735848</v>
       </c>
       <c r="N69">
-        <v>-58.34771120000001</v>
+        <v>-80.97358480000003</v>
       </c>
       <c r="O69">
-        <v>-10.502588016</v>
+        <v>-14.575245264</v>
       </c>
       <c r="P69">
-        <v>-47.845123184</v>
+        <v>-66.39833953600002</v>
       </c>
       <c r="Q69">
-        <v>-15.845123184</v>
+        <v>-34.39833953600002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1413404102642204</v>
+        <v>0.1452750915845388</v>
       </c>
       <c r="T69">
-        <v>1.610948572472663</v>
+        <v>1.677292952181441</v>
       </c>
       <c r="U69">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.09095555895789183</v>
+        <v>0.07631590255924096</v>
       </c>
       <c r="W69">
-        <v>0.1825361237612553</v>
+        <v>0.217804710176531</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.5053086608771769</v>
+        <v>0.4239772364402276</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1945952322270935</v>
+        <v>0.1964952322270935</v>
       </c>
       <c r="C70">
-        <v>-187.8080809845276</v>
+        <v>-199.6707312086758</v>
       </c>
       <c r="D70">
-        <v>318.4479190154725</v>
+        <v>315.3522687913243</v>
       </c>
       <c r="E70">
-        <v>580.1560000000001</v>
+        <v>588.9230000000001</v>
       </c>
       <c r="F70">
-        <v>596.1560000000001</v>
+        <v>604.9230000000001</v>
       </c>
       <c r="G70">
         <v>89.90000000000001</v>
@@ -7027,37 +7027,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M70">
-        <v>140.5735848</v>
+        <v>142.6408434</v>
       </c>
       <c r="N70">
-        <v>-80.97358480000003</v>
+        <v>-83.04084340000003</v>
       </c>
       <c r="O70">
-        <v>-14.575245264</v>
+        <v>-14.947351812</v>
       </c>
       <c r="P70">
-        <v>-66.39833953600002</v>
+        <v>-68.09349158800002</v>
       </c>
       <c r="Q70">
-        <v>-34.39833953600002</v>
+        <v>-36.09349158800002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1452750915845388</v>
+        <v>0.1484839655066207</v>
       </c>
       <c r="T70">
-        <v>1.677292952181441</v>
+        <v>1.731399176445358</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.07631590255924096</v>
+        <v>0.07520987498591863</v>
       </c>
       <c r="W70">
-        <v>0.217804710176531</v>
+        <v>0.2180655114783204</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4239772364402276</v>
+        <v>0.4178326388106591</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1964952322270935</v>
+        <v>0.1983952322270935</v>
       </c>
       <c r="C71">
-        <v>-199.6707312086758</v>
+        <v>-211.4737748897172</v>
       </c>
       <c r="D71">
-        <v>315.3522687913243</v>
+        <v>312.3162251102828</v>
       </c>
       <c r="E71">
-        <v>588.9230000000001</v>
+        <v>597.6900000000001</v>
       </c>
       <c r="F71">
-        <v>604.9230000000001</v>
+        <v>613.6900000000001</v>
       </c>
       <c r="G71">
         <v>89.90000000000001</v>
@@ -7109,37 +7109,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M71">
-        <v>142.6408434</v>
+        <v>144.708102</v>
       </c>
       <c r="N71">
-        <v>-83.04084340000003</v>
+        <v>-85.10810200000003</v>
       </c>
       <c r="O71">
-        <v>-14.947351812</v>
+        <v>-15.31945836000001</v>
       </c>
       <c r="P71">
-        <v>-68.09349158800002</v>
+        <v>-69.78864364000003</v>
       </c>
       <c r="Q71">
-        <v>-36.09349158800002</v>
+        <v>-37.78864364000003</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1484839655066207</v>
+        <v>0.1519067643568414</v>
       </c>
       <c r="T71">
-        <v>1.731399176445358</v>
+        <v>1.78911248232687</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07520987498591863</v>
+        <v>0.0741354482004055</v>
       </c>
       <c r="W71">
-        <v>0.2180655114783204</v>
+        <v>0.2183188613143444</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4178326388106591</v>
+        <v>0.411863601113364</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1983952322270935</v>
+        <v>0.2002952322270935</v>
       </c>
       <c r="C72">
-        <v>-211.4737748897172</v>
+        <v>-223.2189171913922</v>
       </c>
       <c r="D72">
-        <v>312.3162251102828</v>
+        <v>309.338082808608</v>
       </c>
       <c r="E72">
-        <v>597.6900000000001</v>
+        <v>606.4570000000001</v>
       </c>
       <c r="F72">
-        <v>613.6900000000001</v>
+        <v>622.4570000000001</v>
       </c>
       <c r="G72">
         <v>89.90000000000001</v>
@@ -7191,37 +7191,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M72">
-        <v>144.708102</v>
+        <v>146.7753606</v>
       </c>
       <c r="N72">
-        <v>-85.10810200000003</v>
+        <v>-87.17536060000003</v>
       </c>
       <c r="O72">
-        <v>-15.31945836000001</v>
+        <v>-15.69156490800001</v>
       </c>
       <c r="P72">
-        <v>-69.78864364000003</v>
+        <v>-71.48379569200003</v>
       </c>
       <c r="Q72">
-        <v>-37.78864364000003</v>
+        <v>-39.48379569200003</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1519067643568414</v>
+        <v>0.1555656183001808</v>
       </c>
       <c r="T72">
-        <v>1.78911248232687</v>
+        <v>1.850806016200211</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.0741354482004055</v>
+        <v>0.07309128695814628</v>
       </c>
       <c r="W72">
-        <v>0.2183188613143444</v>
+        <v>0.2185650745352691</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.411863601113364</v>
+        <v>0.4060627053230349</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2002952322270935</v>
+        <v>0.2021952322270935</v>
       </c>
       <c r="C73">
-        <v>-223.2189171913921</v>
+        <v>-234.9077988523086</v>
       </c>
       <c r="D73">
-        <v>309.338082808608</v>
+        <v>306.4162011476914</v>
       </c>
       <c r="E73">
-        <v>606.457</v>
+        <v>615.224</v>
       </c>
       <c r="F73">
-        <v>622.457</v>
+        <v>631.224</v>
       </c>
       <c r="G73">
         <v>89.90000000000001</v>
@@ -7273,37 +7273,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M73">
-        <v>146.7753606</v>
+        <v>148.8426192</v>
       </c>
       <c r="N73">
-        <v>-87.1753606</v>
+        <v>-89.24261920000004</v>
       </c>
       <c r="O73">
-        <v>-15.691564908</v>
+        <v>-16.06367145600001</v>
       </c>
       <c r="P73">
-        <v>-71.483795692</v>
+        <v>-73.17894774400003</v>
       </c>
       <c r="Q73">
-        <v>-39.483795692</v>
+        <v>-41.17894774400003</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1555656183001807</v>
+        <v>0.1594858189537586</v>
       </c>
       <c r="T73">
-        <v>1.85080601620021</v>
+        <v>1.916906231064503</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.07309128695814629</v>
+        <v>0.07207613019483869</v>
       </c>
       <c r="W73">
-        <v>0.2185650745352691</v>
+        <v>0.218804448500057</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4060627053230349</v>
+        <v>0.4004229455268816</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2021952322270935</v>
+        <v>0.2040952322270935</v>
       </c>
       <c r="C74">
-        <v>-234.9077988523086</v>
+        <v>-246.5419992001412</v>
       </c>
       <c r="D74">
-        <v>306.4162011476914</v>
+        <v>303.5490007998588</v>
       </c>
       <c r="E74">
-        <v>615.224</v>
+        <v>623.991</v>
       </c>
       <c r="F74">
-        <v>631.224</v>
+        <v>639.991</v>
       </c>
       <c r="G74">
         <v>89.90000000000001</v>
@@ -7355,37 +7355,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M74">
-        <v>148.8426192</v>
+        <v>150.9098778</v>
       </c>
       <c r="N74">
-        <v>-89.24261920000004</v>
+        <v>-91.30987780000001</v>
       </c>
       <c r="O74">
-        <v>-16.06367145600001</v>
+        <v>-16.435778004</v>
       </c>
       <c r="P74">
-        <v>-73.17894774400003</v>
+        <v>-74.87409979600001</v>
       </c>
       <c r="Q74">
-        <v>-41.17894774400003</v>
+        <v>-42.87409979600001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1594858189537586</v>
+        <v>0.1636964048409348</v>
       </c>
       <c r="T74">
-        <v>1.916906231064503</v>
+        <v>1.987902758140966</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.07207613019483869</v>
+        <v>0.07108878594559434</v>
       </c>
       <c r="W74">
-        <v>0.218804448500057</v>
+        <v>0.2190372642740289</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4004229455268816</v>
+        <v>0.3949376996977463</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2040952322270935</v>
+        <v>0.2059952322270935</v>
       </c>
       <c r="C75">
-        <v>-246.5419992001412</v>
+        <v>-258.1230389981681</v>
       </c>
       <c r="D75">
-        <v>303.5490007998588</v>
+        <v>300.7349610018319</v>
       </c>
       <c r="E75">
-        <v>623.991</v>
+        <v>632.758</v>
       </c>
       <c r="F75">
-        <v>639.991</v>
+        <v>648.758</v>
       </c>
       <c r="G75">
         <v>89.90000000000001</v>
@@ -7437,37 +7437,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M75">
-        <v>150.9098778</v>
+        <v>152.9771364</v>
       </c>
       <c r="N75">
-        <v>-91.30987780000001</v>
+        <v>-93.37713640000001</v>
       </c>
       <c r="O75">
-        <v>-16.435778004</v>
+        <v>-16.807884552</v>
       </c>
       <c r="P75">
-        <v>-74.87409979600001</v>
+        <v>-76.56925184800001</v>
       </c>
       <c r="Q75">
-        <v>-42.87409979600001</v>
+        <v>-44.56925184800001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1636964048409348</v>
+        <v>0.1682308819502016</v>
       </c>
       <c r="T75">
-        <v>1.987902758140966</v>
+        <v>2.064360556531003</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07108878594559434</v>
+        <v>0.07012812667605926</v>
       </c>
       <c r="W75">
-        <v>0.2190372642740289</v>
+        <v>0.2192637877297852</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3949376996977463</v>
+        <v>0.3896007037558848</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2059952322270935</v>
+        <v>0.2078952322270935</v>
       </c>
       <c r="C76">
-        <v>-258.1230389981681</v>
+        <v>-269.6523831349338</v>
       </c>
       <c r="D76">
-        <v>300.7349610018319</v>
+        <v>297.9726168650664</v>
       </c>
       <c r="E76">
-        <v>632.758</v>
+        <v>641.5250000000001</v>
       </c>
       <c r="F76">
-        <v>648.758</v>
+        <v>657.5250000000001</v>
       </c>
       <c r="G76">
         <v>89.90000000000001</v>
@@ -7519,37 +7519,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M76">
-        <v>152.9771364</v>
+        <v>155.044395</v>
       </c>
       <c r="N76">
-        <v>-93.37713640000001</v>
+        <v>-95.44439500000004</v>
       </c>
       <c r="O76">
-        <v>-16.807884552</v>
+        <v>-17.17999110000001</v>
       </c>
       <c r="P76">
-        <v>-76.56925184800001</v>
+        <v>-78.26440390000003</v>
       </c>
       <c r="Q76">
-        <v>-44.56925184800001</v>
+        <v>-46.26440390000003</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1682308819502016</v>
+        <v>0.1731281172282096</v>
       </c>
       <c r="T76">
-        <v>2.064360556531003</v>
+        <v>2.146934978792244</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.07012812667605926</v>
+        <v>0.06919308498704514</v>
       </c>
       <c r="W76">
-        <v>0.2192637877297852</v>
+        <v>0.2194842705600548</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3896007037558848</v>
+        <v>0.3844060277058063</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2078952322270935</v>
+        <v>0.2097952322270935</v>
       </c>
       <c r="C77">
-        <v>-269.6523831349338</v>
+        <v>-281.1314431670253</v>
       </c>
       <c r="D77">
-        <v>297.9726168650664</v>
+        <v>295.2605568329747</v>
       </c>
       <c r="E77">
-        <v>641.5250000000001</v>
+        <v>650.292</v>
       </c>
       <c r="F77">
-        <v>657.5250000000001</v>
+        <v>666.292</v>
       </c>
       <c r="G77">
         <v>89.90000000000001</v>
@@ -7601,37 +7601,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M77">
-        <v>155.044395</v>
+        <v>157.1116536</v>
       </c>
       <c r="N77">
-        <v>-95.44439500000004</v>
+        <v>-97.51165360000002</v>
       </c>
       <c r="O77">
-        <v>-17.17999110000001</v>
+        <v>-17.552097648</v>
       </c>
       <c r="P77">
-        <v>-78.26440390000003</v>
+        <v>-79.95955595200002</v>
       </c>
       <c r="Q77">
-        <v>-46.26440390000003</v>
+        <v>-47.95955595200002</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1731281172282096</v>
+        <v>0.1784334554460517</v>
       </c>
       <c r="T77">
-        <v>2.146934978792244</v>
+        <v>2.236390602908588</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06919308498704514</v>
+        <v>0.06828264965826823</v>
       </c>
       <c r="W77">
-        <v>0.2194842705600548</v>
+        <v>0.2196989512105804</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3844060277058063</v>
+        <v>0.3793480536570458</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2097952322270935</v>
+        <v>0.2116952322270935</v>
       </c>
       <c r="C78">
-        <v>-281.1314431670253</v>
+        <v>-292.5615797242425</v>
       </c>
       <c r="D78">
-        <v>295.2605568329747</v>
+        <v>292.5974202757576</v>
       </c>
       <c r="E78">
-        <v>650.292</v>
+        <v>659.0590000000001</v>
       </c>
       <c r="F78">
-        <v>666.292</v>
+        <v>675.0590000000001</v>
       </c>
       <c r="G78">
         <v>89.90000000000001</v>
@@ -7683,37 +7683,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M78">
-        <v>157.1116536</v>
+        <v>159.1789122</v>
       </c>
       <c r="N78">
-        <v>-97.51165360000002</v>
+        <v>-99.57891220000002</v>
       </c>
       <c r="O78">
-        <v>-17.552097648</v>
+        <v>-17.924204196</v>
       </c>
       <c r="P78">
-        <v>-79.95955595200002</v>
+        <v>-81.65470800400001</v>
       </c>
       <c r="Q78">
-        <v>-47.95955595200002</v>
+        <v>-49.65470800400001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1784334554460517</v>
+        <v>0.184200127421967</v>
       </c>
       <c r="T78">
-        <v>2.236390602908588</v>
+        <v>2.333624976948091</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06828264965826823</v>
+        <v>0.06739586200036865</v>
       </c>
       <c r="W78">
-        <v>0.2196989512105804</v>
+        <v>0.2199080557403131</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3793480536570458</v>
+        <v>0.3744214555576036</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2116952322270935</v>
+        <v>0.2135952322270935</v>
       </c>
       <c r="C79">
-        <v>-292.5615797242425</v>
+        <v>-303.9441047857662</v>
       </c>
       <c r="D79">
-        <v>292.5974202757576</v>
+        <v>289.9818952142339</v>
       </c>
       <c r="E79">
-        <v>659.0590000000001</v>
+        <v>667.826</v>
       </c>
       <c r="F79">
-        <v>675.0590000000001</v>
+        <v>683.826</v>
       </c>
       <c r="G79">
         <v>89.90000000000001</v>
@@ -7765,37 +7765,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M79">
-        <v>159.1789122</v>
+        <v>161.2461708</v>
       </c>
       <c r="N79">
-        <v>-99.57891220000002</v>
+        <v>-101.6461708</v>
       </c>
       <c r="O79">
-        <v>-17.924204196</v>
+        <v>-18.296310744</v>
       </c>
       <c r="P79">
-        <v>-81.65470800400001</v>
+        <v>-83.34986005600001</v>
       </c>
       <c r="Q79">
-        <v>-49.65470800400001</v>
+        <v>-51.34986005600001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.184200127421967</v>
+        <v>0.1904910423047837</v>
       </c>
       <c r="T79">
-        <v>2.333624976948091</v>
+        <v>2.439698839536641</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06739586200036865</v>
+        <v>0.0665318124875434</v>
       </c>
       <c r="W79">
-        <v>0.2199080557403131</v>
+        <v>0.2201117986154373</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3744214555576036</v>
+        <v>0.3696211804863523</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2135952322270935</v>
+        <v>0.2154952322270935</v>
       </c>
       <c r="C80">
-        <v>-303.9441047857662</v>
+        <v>-315.2802838353315</v>
       </c>
       <c r="D80">
-        <v>289.9818952142339</v>
+        <v>287.4127161646686</v>
       </c>
       <c r="E80">
-        <v>667.826</v>
+        <v>676.5930000000001</v>
       </c>
       <c r="F80">
-        <v>683.826</v>
+        <v>692.5930000000001</v>
       </c>
       <c r="G80">
         <v>89.90000000000001</v>
@@ -7847,37 +7847,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M80">
-        <v>161.2461708</v>
+        <v>163.3134294</v>
       </c>
       <c r="N80">
-        <v>-101.6461708</v>
+        <v>-103.7134294</v>
       </c>
       <c r="O80">
-        <v>-18.296310744</v>
+        <v>-18.668417292</v>
       </c>
       <c r="P80">
-        <v>-83.34986005600001</v>
+        <v>-85.04501210800002</v>
       </c>
       <c r="Q80">
-        <v>-51.34986005600001</v>
+        <v>-53.04501210800002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1904910423047837</v>
+        <v>0.1973810919383448</v>
       </c>
       <c r="T80">
-        <v>2.439698839536641</v>
+        <v>2.555874974752672</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.0665318124875434</v>
+        <v>0.06568963764592893</v>
       </c>
       <c r="W80">
-        <v>0.2201117986154373</v>
+        <v>0.22031038344309</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3696211804863523</v>
+        <v>0.3649424313662719</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2154952322270935</v>
+        <v>0.2173952322270935</v>
       </c>
       <c r="C81">
-        <v>-315.2802838353315</v>
+        <v>-326.5713379028381</v>
       </c>
       <c r="D81">
-        <v>287.4127161646686</v>
+        <v>284.8886620971621</v>
       </c>
       <c r="E81">
-        <v>676.5930000000001</v>
+        <v>685.3600000000001</v>
       </c>
       <c r="F81">
-        <v>692.5930000000001</v>
+        <v>701.3600000000001</v>
       </c>
       <c r="G81">
         <v>89.90000000000001</v>
@@ -7929,37 +7929,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M81">
-        <v>163.3134294</v>
+        <v>165.380688</v>
       </c>
       <c r="N81">
-        <v>-103.7134294</v>
+        <v>-105.7806880000001</v>
       </c>
       <c r="O81">
-        <v>-18.668417292</v>
+        <v>-19.04052384000001</v>
       </c>
       <c r="P81">
-        <v>-85.04501210800002</v>
+        <v>-86.74016416000005</v>
       </c>
       <c r="Q81">
-        <v>-53.04501210800002</v>
+        <v>-54.74016416000005</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1973810919383448</v>
+        <v>0.2049601465352621</v>
       </c>
       <c r="T81">
-        <v>2.555874974752672</v>
+        <v>2.683668723490305</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06568963764592893</v>
+        <v>0.06486851717535481</v>
       </c>
       <c r="W81">
-        <v>0.22031038344309</v>
+        <v>0.2205040036500514</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3649424313662719</v>
+        <v>0.3603806509741934</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2173952322270935</v>
+        <v>0.2192952322270935</v>
       </c>
       <c r="C82">
-        <v>-326.5713379028381</v>
+        <v>-337.8184454993219</v>
       </c>
       <c r="D82">
-        <v>284.8886620971621</v>
+        <v>282.4085545006782</v>
       </c>
       <c r="E82">
-        <v>685.3600000000001</v>
+        <v>694.1270000000001</v>
       </c>
       <c r="F82">
-        <v>701.3600000000001</v>
+        <v>710.1270000000001</v>
       </c>
       <c r="G82">
         <v>89.90000000000001</v>
@@ -8011,37 +8011,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M82">
-        <v>165.380688</v>
+        <v>167.4479466</v>
       </c>
       <c r="N82">
-        <v>-105.7806880000001</v>
+        <v>-107.8479466</v>
       </c>
       <c r="O82">
-        <v>-19.04052384000001</v>
+        <v>-19.412630388</v>
       </c>
       <c r="P82">
-        <v>-86.74016416000005</v>
+        <v>-88.43531621200003</v>
       </c>
       <c r="Q82">
-        <v>-54.74016416000005</v>
+        <v>-56.43531621200003</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2049601465352621</v>
+        <v>0.2133369963529075</v>
       </c>
       <c r="T82">
-        <v>2.683668723490305</v>
+        <v>2.824914445779269</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06486851717535481</v>
+        <v>0.06406767128430106</v>
       </c>
       <c r="W82">
-        <v>0.2205040036500514</v>
+        <v>0.2206928431111618</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3603806509741934</v>
+        <v>0.3559315071350059</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2192952322270935</v>
+        <v>0.2211952322270935</v>
       </c>
       <c r="C83">
-        <v>-337.8184454993219</v>
+        <v>-349.02274445173</v>
       </c>
       <c r="D83">
-        <v>282.4085545006782</v>
+        <v>279.9712555482701</v>
       </c>
       <c r="E83">
-        <v>694.1270000000001</v>
+        <v>702.8940000000001</v>
       </c>
       <c r="F83">
-        <v>710.1270000000001</v>
+        <v>718.8940000000001</v>
       </c>
       <c r="G83">
         <v>89.90000000000001</v>
@@ -8093,37 +8093,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M83">
-        <v>167.4479466</v>
+        <v>169.5152052</v>
       </c>
       <c r="N83">
-        <v>-107.8479466</v>
+        <v>-109.9152052</v>
       </c>
       <c r="O83">
-        <v>-19.412630388</v>
+        <v>-19.78473693600001</v>
       </c>
       <c r="P83">
-        <v>-88.43531621200003</v>
+        <v>-90.13046826400003</v>
       </c>
       <c r="Q83">
-        <v>-56.43531621200003</v>
+        <v>-58.13046826400003</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2133369963529075</v>
+        <v>0.2226446072614023</v>
       </c>
       <c r="T83">
-        <v>2.824914445779269</v>
+        <v>2.98185413721145</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06406767128430106</v>
+        <v>0.06328635821985837</v>
       </c>
       <c r="W83">
-        <v>0.2206928431111618</v>
+        <v>0.2208770767317574</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3559315071350059</v>
+        <v>0.3515908789992132</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2211952322270935</v>
+        <v>0.2230952322270935</v>
       </c>
       <c r="C84">
-        <v>-349.02274445173</v>
+        <v>-360.1853336434982</v>
       </c>
       <c r="D84">
-        <v>279.9712555482701</v>
+        <v>277.5756663565019</v>
       </c>
       <c r="E84">
-        <v>702.8940000000001</v>
+        <v>711.6610000000001</v>
       </c>
       <c r="F84">
-        <v>718.8940000000001</v>
+        <v>727.6610000000001</v>
       </c>
       <c r="G84">
         <v>89.90000000000001</v>
@@ -8175,37 +8175,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M84">
-        <v>169.5152052</v>
+        <v>171.5824638</v>
       </c>
       <c r="N84">
-        <v>-109.9152052</v>
+        <v>-111.9824638</v>
       </c>
       <c r="O84">
-        <v>-19.78473693600001</v>
+        <v>-20.15684348400001</v>
       </c>
       <c r="P84">
-        <v>-90.13046826400003</v>
+        <v>-91.82562031600003</v>
       </c>
       <c r="Q84">
-        <v>-58.13046826400003</v>
+        <v>-59.82562031600003</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2226446072614023</v>
+        <v>0.2330472312179554</v>
       </c>
       <c r="T84">
-        <v>2.98185413721145</v>
+        <v>3.1572573217533</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06328635821985837</v>
+        <v>0.06252387197624561</v>
       </c>
       <c r="W84">
-        <v>0.2208770767317574</v>
+        <v>0.2210568709880013</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3515908789992132</v>
+        <v>0.3473548443124757</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2230952322270935</v>
+        <v>0.2249952322270935</v>
       </c>
       <c r="C85">
-        <v>-360.1853336434982</v>
+        <v>-371.307274666527</v>
       </c>
       <c r="D85">
-        <v>277.5756663565019</v>
+        <v>275.2207253334731</v>
       </c>
       <c r="E85">
-        <v>711.6610000000001</v>
+        <v>720.4280000000001</v>
       </c>
       <c r="F85">
-        <v>727.6610000000001</v>
+        <v>736.4280000000001</v>
       </c>
       <c r="G85">
         <v>89.90000000000001</v>
@@ -8257,37 +8257,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M85">
-        <v>171.5824638</v>
+        <v>173.6497224</v>
       </c>
       <c r="N85">
-        <v>-111.9824638</v>
+        <v>-114.0497224</v>
       </c>
       <c r="O85">
-        <v>-20.15684348400001</v>
+        <v>-20.528950032</v>
       </c>
       <c r="P85">
-        <v>-91.82562031600003</v>
+        <v>-93.52077236800002</v>
       </c>
       <c r="Q85">
-        <v>-59.82562031600003</v>
+        <v>-61.52077236800002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2330472312179554</v>
+        <v>0.2447501831690777</v>
       </c>
       <c r="T85">
-        <v>3.1572573217533</v>
+        <v>3.354585904362883</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06252387197624561</v>
+        <v>0.06177954016700459</v>
       </c>
       <c r="W85">
-        <v>0.2210568709880013</v>
+        <v>0.2212323844286203</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3473548443124757</v>
+        <v>0.34321966759447</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2249952322270935</v>
+        <v>0.2268952322270935</v>
       </c>
       <c r="C86">
-        <v>-371.3072746665268</v>
+        <v>-382.389593389773</v>
       </c>
       <c r="D86">
-        <v>275.2207253334731</v>
+        <v>272.905406610227</v>
       </c>
       <c r="E86">
-        <v>720.428</v>
+        <v>729.1950000000001</v>
       </c>
       <c r="F86">
-        <v>736.428</v>
+        <v>745.1950000000001</v>
       </c>
       <c r="G86">
         <v>89.90000000000001</v>
@@ -8339,37 +8339,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M86">
-        <v>173.6497224</v>
+        <v>175.716981</v>
       </c>
       <c r="N86">
-        <v>-114.0497224</v>
+        <v>-116.116981</v>
       </c>
       <c r="O86">
-        <v>-20.528950032</v>
+        <v>-20.90105658000001</v>
       </c>
       <c r="P86">
-        <v>-93.52077236800001</v>
+        <v>-95.21592442000004</v>
       </c>
       <c r="Q86">
-        <v>-61.52077236800001</v>
+        <v>-63.21592442000004</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2447501831690775</v>
+        <v>0.2580135287136827</v>
       </c>
       <c r="T86">
-        <v>3.35458590436288</v>
+        <v>3.578224964653739</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06177954016700461</v>
+        <v>0.06105272204739277</v>
       </c>
       <c r="W86">
-        <v>0.2212323844286203</v>
+        <v>0.2214037681412248</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.34321966759447</v>
+        <v>0.3391817891521821</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2268952322270935</v>
+        <v>0.2287952322270935</v>
       </c>
       <c r="C87">
-        <v>-382.389593389773</v>
+        <v>-393.433281449327</v>
       </c>
       <c r="D87">
-        <v>272.905406610227</v>
+        <v>270.6287185506731</v>
       </c>
       <c r="E87">
-        <v>729.1950000000001</v>
+        <v>737.962</v>
       </c>
       <c r="F87">
-        <v>745.1950000000001</v>
+        <v>753.962</v>
       </c>
       <c r="G87">
         <v>89.90000000000001</v>
@@ -8421,37 +8421,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M87">
-        <v>175.716981</v>
+        <v>177.7842396</v>
       </c>
       <c r="N87">
-        <v>-116.116981</v>
+        <v>-118.1842396</v>
       </c>
       <c r="O87">
-        <v>-20.90105658000001</v>
+        <v>-21.273163128</v>
       </c>
       <c r="P87">
-        <v>-95.21592442000004</v>
+        <v>-96.91107647200002</v>
       </c>
       <c r="Q87">
-        <v>-63.21592442000004</v>
+        <v>-64.91107647200002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2580135287136827</v>
+        <v>0.2731716379075171</v>
       </c>
       <c r="T87">
-        <v>3.578224964653739</v>
+        <v>3.833812462129006</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06105272204739277</v>
+        <v>0.06034280667474867</v>
       </c>
       <c r="W87">
-        <v>0.2214037681412248</v>
+        <v>0.2215711661860943</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3391817891521821</v>
+        <v>0.3352378148597149</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2287952322270935</v>
+        <v>0.2306952322270935</v>
       </c>
       <c r="C88">
-        <v>-393.433281449327</v>
+        <v>-404.4392976645211</v>
       </c>
       <c r="D88">
-        <v>270.6287185506731</v>
+        <v>268.3897023354789</v>
       </c>
       <c r="E88">
-        <v>737.962</v>
+        <v>746.729</v>
       </c>
       <c r="F88">
-        <v>753.962</v>
+        <v>762.729</v>
       </c>
       <c r="G88">
         <v>89.90000000000001</v>
@@ -8503,37 +8503,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M88">
-        <v>177.7842396</v>
+        <v>179.8514982</v>
       </c>
       <c r="N88">
-        <v>-118.1842396</v>
+        <v>-120.2514982</v>
       </c>
       <c r="O88">
-        <v>-21.273163128</v>
+        <v>-21.645269676</v>
       </c>
       <c r="P88">
-        <v>-96.91107647200002</v>
+        <v>-98.60622852400002</v>
       </c>
       <c r="Q88">
-        <v>-64.91107647200002</v>
+        <v>-66.60622852400002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2731716379075171</v>
+        <v>0.2906617639004031</v>
       </c>
       <c r="T88">
-        <v>3.833812462129006</v>
+        <v>4.128721113062007</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06034280667474867</v>
+        <v>0.05964921119572858</v>
       </c>
       <c r="W88">
-        <v>0.2215711661860943</v>
+        <v>0.2217347160000472</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3352378148597149</v>
+        <v>0.3313845066429365</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2306952322270935</v>
+        <v>0.2325952322270935</v>
       </c>
       <c r="C89">
-        <v>-404.4392976645211</v>
+        <v>-415.4085693843193</v>
       </c>
       <c r="D89">
-        <v>268.3897023354789</v>
+        <v>266.1874306156808</v>
       </c>
       <c r="E89">
-        <v>746.729</v>
+        <v>755.4960000000001</v>
       </c>
       <c r="F89">
-        <v>762.729</v>
+        <v>771.4960000000001</v>
       </c>
       <c r="G89">
         <v>89.90000000000001</v>
@@ -8585,37 +8585,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M89">
-        <v>179.8514982</v>
+        <v>181.9187568</v>
       </c>
       <c r="N89">
-        <v>-120.2514982</v>
+        <v>-122.3187568</v>
       </c>
       <c r="O89">
-        <v>-21.645269676</v>
+        <v>-22.01737622400001</v>
       </c>
       <c r="P89">
-        <v>-98.60622852400002</v>
+        <v>-100.301380576</v>
       </c>
       <c r="Q89">
-        <v>-66.60622852400002</v>
+        <v>-68.30138057600004</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2906617639004031</v>
+        <v>0.3110669108921034</v>
       </c>
       <c r="T89">
-        <v>4.128721113062007</v>
+        <v>4.472781205817174</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05964921119572858</v>
+        <v>0.05897137925032257</v>
       </c>
       <c r="W89">
-        <v>0.2217347160000472</v>
+        <v>0.221894548772774</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3313845066429365</v>
+        <v>0.3276187736129031</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2325952322270935</v>
+        <v>0.2344952322270935</v>
       </c>
       <c r="C90">
-        <v>-415.4085693843193</v>
+        <v>-426.3419937679593</v>
       </c>
       <c r="D90">
-        <v>266.1874306156808</v>
+        <v>264.0210062320408</v>
       </c>
       <c r="E90">
-        <v>755.4960000000001</v>
+        <v>764.263</v>
       </c>
       <c r="F90">
-        <v>771.4960000000001</v>
+        <v>780.263</v>
       </c>
       <c r="G90">
         <v>89.90000000000001</v>
@@ -8667,37 +8667,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M90">
-        <v>181.9187568</v>
+        <v>183.9860154</v>
       </c>
       <c r="N90">
-        <v>-122.3187568</v>
+        <v>-124.3860154</v>
       </c>
       <c r="O90">
-        <v>-22.01737622400001</v>
+        <v>-22.389482772</v>
       </c>
       <c r="P90">
-        <v>-100.301380576</v>
+        <v>-101.996532628</v>
       </c>
       <c r="Q90">
-        <v>-68.30138057600004</v>
+        <v>-69.99653262800001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3110669108921034</v>
+        <v>0.3351820846095673</v>
       </c>
       <c r="T90">
-        <v>4.472781205817174</v>
+        <v>4.879397679073281</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05897137925032257</v>
+        <v>0.05830877948346502</v>
       </c>
       <c r="W90">
-        <v>0.221894548772774</v>
+        <v>0.222050789797799</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3276187736129031</v>
+        <v>0.3239376637970278</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2344952322270935</v>
+        <v>0.2363952322270935</v>
       </c>
       <c r="C91">
-        <v>-426.3419937679593</v>
+        <v>-437.2404390035633</v>
       </c>
       <c r="D91">
-        <v>264.0210062320408</v>
+        <v>261.8895609964368</v>
       </c>
       <c r="E91">
-        <v>764.263</v>
+        <v>773.0300000000001</v>
       </c>
       <c r="F91">
-        <v>780.263</v>
+        <v>789.0300000000001</v>
       </c>
       <c r="G91">
         <v>89.90000000000001</v>
@@ -8749,37 +8749,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M91">
-        <v>183.9860154</v>
+        <v>186.053274</v>
       </c>
       <c r="N91">
-        <v>-124.3860154</v>
+        <v>-126.453274</v>
       </c>
       <c r="O91">
-        <v>-22.389482772</v>
+        <v>-22.76158932</v>
       </c>
       <c r="P91">
-        <v>-101.996532628</v>
+        <v>-103.69168468</v>
       </c>
       <c r="Q91">
-        <v>-69.99653262800001</v>
+        <v>-71.69168468000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3351820846095673</v>
+        <v>0.3641202930705241</v>
       </c>
       <c r="T91">
-        <v>4.879397679073281</v>
+        <v>5.36733744698061</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05830877948346502</v>
+        <v>0.05766090415587095</v>
       </c>
       <c r="W91">
-        <v>0.222050789797799</v>
+        <v>0.2222035588000456</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3239376637970278</v>
+        <v>0.3203383564215053</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2363952322270935</v>
+        <v>0.2382952322270935</v>
       </c>
       <c r="C92">
-        <v>-437.2404390035633</v>
+        <v>-448.1047454681935</v>
       </c>
       <c r="D92">
-        <v>261.8895609964368</v>
+        <v>259.7922545318065</v>
       </c>
       <c r="E92">
-        <v>773.0300000000001</v>
+        <v>781.797</v>
       </c>
       <c r="F92">
-        <v>789.0300000000001</v>
+        <v>797.797</v>
       </c>
       <c r="G92">
         <v>89.90000000000001</v>
@@ -8831,37 +8831,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M92">
-        <v>186.053274</v>
+        <v>188.1205326</v>
       </c>
       <c r="N92">
-        <v>-126.453274</v>
+        <v>-128.5205326</v>
       </c>
       <c r="O92">
-        <v>-22.76158932</v>
+        <v>-23.133695868</v>
       </c>
       <c r="P92">
-        <v>-103.69168468</v>
+        <v>-105.386836732</v>
       </c>
       <c r="Q92">
-        <v>-71.69168468000002</v>
+        <v>-73.38683673200002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3641202930705241</v>
+        <v>0.3994892145228046</v>
       </c>
       <c r="T92">
-        <v>5.36733744698061</v>
+        <v>5.963708274422901</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05766090415587095</v>
+        <v>0.05702726784646578</v>
       </c>
       <c r="W92">
-        <v>0.2222035588000456</v>
+        <v>0.2223529702418034</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3203383564215053</v>
+        <v>0.3168181547025877</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2382952322270935</v>
+        <v>0.2401952322270935</v>
       </c>
       <c r="C93">
-        <v>-448.1047454681935</v>
+        <v>-458.9357268326104</v>
       </c>
       <c r="D93">
-        <v>259.7922545318065</v>
+        <v>257.7282731673897</v>
       </c>
       <c r="E93">
-        <v>781.797</v>
+        <v>790.5640000000001</v>
       </c>
       <c r="F93">
-        <v>797.797</v>
+        <v>806.5640000000001</v>
       </c>
       <c r="G93">
         <v>89.90000000000001</v>
@@ -8913,37 +8913,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M93">
-        <v>188.1205326</v>
+        <v>190.1877912</v>
       </c>
       <c r="N93">
-        <v>-128.5205326</v>
+        <v>-130.5877912</v>
       </c>
       <c r="O93">
-        <v>-23.133695868</v>
+        <v>-23.50580241600001</v>
       </c>
       <c r="P93">
-        <v>-105.386836732</v>
+        <v>-107.081988784</v>
       </c>
       <c r="Q93">
-        <v>-73.38683673200002</v>
+        <v>-75.08198878400002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3994892145228046</v>
+        <v>0.4437003663381553</v>
       </c>
       <c r="T93">
-        <v>5.963708274422901</v>
+        <v>6.709171808725765</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05702726784646578</v>
+        <v>0.05640740623943898</v>
       </c>
       <c r="W93">
-        <v>0.2223529702418034</v>
+        <v>0.2224991336087403</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3168181547025877</v>
+        <v>0.3133744791079943</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2401952322270935</v>
+        <v>0.2420952322270935</v>
       </c>
       <c r="C94">
-        <v>-458.9357268326104</v>
+        <v>-469.7341711137833</v>
       </c>
       <c r="D94">
-        <v>257.7282731673897</v>
+        <v>255.6968288862168</v>
       </c>
       <c r="E94">
-        <v>790.5640000000001</v>
+        <v>799.3310000000001</v>
       </c>
       <c r="F94">
-        <v>806.5640000000001</v>
+        <v>815.3310000000001</v>
       </c>
       <c r="G94">
         <v>89.90000000000001</v>
@@ -8995,37 +8995,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M94">
-        <v>190.1877912</v>
+        <v>192.2550498000001</v>
       </c>
       <c r="N94">
-        <v>-130.5877912</v>
+        <v>-132.6550498000001</v>
       </c>
       <c r="O94">
-        <v>-23.50580241600001</v>
+        <v>-23.87790896400001</v>
       </c>
       <c r="P94">
-        <v>-107.081988784</v>
+        <v>-108.777140836</v>
       </c>
       <c r="Q94">
-        <v>-75.08198878400002</v>
+        <v>-76.77714083600004</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4437003663381553</v>
+        <v>0.5005432758150347</v>
       </c>
       <c r="T94">
-        <v>6.709171808725765</v>
+        <v>7.667624924258019</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05640740623943898</v>
+        <v>0.05580087498955253</v>
       </c>
       <c r="W94">
-        <v>0.2224991336087403</v>
+        <v>0.2226421536774635</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3133744791079943</v>
+        <v>0.3100048610530696</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2420952322270935</v>
+        <v>0.2439952322270935</v>
       </c>
       <c r="C95">
-        <v>-469.7341711137833</v>
+        <v>-480.5008416780145</v>
       </c>
       <c r="D95">
-        <v>255.6968288862168</v>
+        <v>253.6971583219855</v>
       </c>
       <c r="E95">
-        <v>799.3310000000001</v>
+        <v>808.0980000000001</v>
       </c>
       <c r="F95">
-        <v>815.3310000000001</v>
+        <v>824.0980000000001</v>
       </c>
       <c r="G95">
         <v>89.90000000000001</v>
@@ -9077,37 +9077,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M95">
-        <v>192.2550498000001</v>
+        <v>194.3223084</v>
       </c>
       <c r="N95">
-        <v>-132.6550498000001</v>
+        <v>-134.7223084</v>
       </c>
       <c r="O95">
-        <v>-23.87790896400001</v>
+        <v>-24.250015512</v>
       </c>
       <c r="P95">
-        <v>-108.777140836</v>
+        <v>-110.472292888</v>
       </c>
       <c r="Q95">
-        <v>-76.77714083600004</v>
+        <v>-78.47229288800003</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5005432758150347</v>
+        <v>0.5763338217842072</v>
       </c>
       <c r="T95">
-        <v>7.667624924258019</v>
+        <v>8.945562411634358</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05580087498955253</v>
+        <v>0.05520724865987645</v>
       </c>
       <c r="W95">
-        <v>0.2226421536774635</v>
+        <v>0.2227821307660011</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3100048610530696</v>
+        <v>0.3067069369993136</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2439952322270935</v>
+        <v>0.2458952322270935</v>
       </c>
       <c r="C96">
-        <v>-480.5008416780145</v>
+        <v>-491.2364781973599</v>
       </c>
       <c r="D96">
-        <v>253.6971583219855</v>
+        <v>251.7285218026402</v>
       </c>
       <c r="E96">
-        <v>808.0980000000001</v>
+        <v>816.8650000000001</v>
       </c>
       <c r="F96">
-        <v>824.0980000000001</v>
+        <v>832.8650000000001</v>
       </c>
       <c r="G96">
         <v>89.90000000000001</v>
@@ -9159,37 +9159,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M96">
-        <v>194.3223084</v>
+        <v>196.389567</v>
       </c>
       <c r="N96">
-        <v>-134.7223084</v>
+        <v>-136.789567</v>
       </c>
       <c r="O96">
-        <v>-24.250015512</v>
+        <v>-24.62212206000001</v>
       </c>
       <c r="P96">
-        <v>-110.472292888</v>
+        <v>-112.16744494</v>
       </c>
       <c r="Q96">
-        <v>-78.47229288800003</v>
+        <v>-80.16744494000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5763338217842072</v>
+        <v>0.682440586141049</v>
       </c>
       <c r="T96">
-        <v>8.945562411634358</v>
+        <v>10.73467489396123</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05520724865987645</v>
+        <v>0.05462611972661458</v>
       </c>
       <c r="W96">
-        <v>0.2227821307660011</v>
+        <v>0.2229191609684643</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3067069369993136</v>
+        <v>0.3034784429256366</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2458952322270935</v>
+        <v>0.2477952322270935</v>
       </c>
       <c r="C97">
-        <v>-491.2364781973599</v>
+        <v>-501.9417975618609</v>
       </c>
       <c r="D97">
-        <v>251.7285218026402</v>
+        <v>249.7902024381392</v>
       </c>
       <c r="E97">
-        <v>816.8650000000001</v>
+        <v>825.6320000000001</v>
       </c>
       <c r="F97">
-        <v>832.8650000000001</v>
+        <v>841.6320000000001</v>
       </c>
       <c r="G97">
         <v>89.90000000000001</v>
@@ -9241,37 +9241,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M97">
-        <v>196.389567</v>
+        <v>198.4568256</v>
       </c>
       <c r="N97">
-        <v>-136.789567</v>
+        <v>-138.8568256</v>
       </c>
       <c r="O97">
-        <v>-24.62212206000001</v>
+        <v>-24.994228608</v>
       </c>
       <c r="P97">
-        <v>-112.16744494</v>
+        <v>-113.862596992</v>
       </c>
       <c r="Q97">
-        <v>-80.16744494000002</v>
+        <v>-81.86259699200004</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.682440586141049</v>
+        <v>0.8416007326763117</v>
       </c>
       <c r="T97">
-        <v>10.73467489396123</v>
+        <v>13.41834361745155</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05462611972661458</v>
+        <v>0.05405709764612902</v>
       </c>
       <c r="W97">
-        <v>0.2229191609684643</v>
+        <v>0.2230533363750428</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3034784429256366</v>
+        <v>0.3003172091451612</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2477952322270935</v>
+        <v>0.2496952322270935</v>
       </c>
       <c r="C98">
-        <v>-501.9417975618609</v>
+        <v>-512.6174947499551</v>
       </c>
       <c r="D98">
-        <v>249.7902024381392</v>
+        <v>247.881505250045</v>
       </c>
       <c r="E98">
-        <v>825.6320000000001</v>
+        <v>834.399</v>
       </c>
       <c r="F98">
-        <v>841.6320000000001</v>
+        <v>850.399</v>
       </c>
       <c r="G98">
         <v>89.90000000000001</v>
@@ -9323,37 +9323,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M98">
-        <v>198.4568256</v>
+        <v>200.5240842</v>
       </c>
       <c r="N98">
-        <v>-138.8568256</v>
+        <v>-140.9240842</v>
       </c>
       <c r="O98">
-        <v>-24.994228608</v>
+        <v>-25.366335156</v>
       </c>
       <c r="P98">
-        <v>-113.862596992</v>
+        <v>-115.557749044</v>
       </c>
       <c r="Q98">
-        <v>-81.86259699200004</v>
+        <v>-83.557749044</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8416007326763095</v>
+        <v>1.106867643568413</v>
       </c>
       <c r="T98">
-        <v>13.41834361745151</v>
+        <v>17.89112482326868</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05405709764612902</v>
+        <v>0.05349980797967409</v>
       </c>
       <c r="W98">
-        <v>0.2230533363750428</v>
+        <v>0.2231847452783929</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3003172091451612</v>
+        <v>0.2972211554426338</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2496952322270935</v>
+        <v>0.2515952322270935</v>
       </c>
       <c r="C99">
-        <v>-512.6174947499551</v>
+        <v>-523.2642436592826</v>
       </c>
       <c r="D99">
-        <v>247.881505250045</v>
+        <v>246.0017563407175</v>
       </c>
       <c r="E99">
-        <v>834.399</v>
+        <v>843.1660000000001</v>
       </c>
       <c r="F99">
-        <v>850.399</v>
+        <v>859.1660000000001</v>
       </c>
       <c r="G99">
         <v>89.90000000000001</v>
@@ -9405,37 +9405,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M99">
-        <v>200.5240842</v>
+        <v>202.5913428</v>
       </c>
       <c r="N99">
-        <v>-140.9240842</v>
+        <v>-142.9913428</v>
       </c>
       <c r="O99">
-        <v>-25.366335156</v>
+        <v>-25.738441704</v>
       </c>
       <c r="P99">
-        <v>-115.557749044</v>
+        <v>-117.252901096</v>
       </c>
       <c r="Q99">
-        <v>-83.557749044</v>
+        <v>-85.25290109600002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.106867643568413</v>
+        <v>1.637401465352619</v>
       </c>
       <c r="T99">
-        <v>17.89112482326868</v>
+        <v>26.83668723490302</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05349980797967409</v>
+        <v>0.05295389157171822</v>
       </c>
       <c r="W99">
-        <v>0.2231847452783929</v>
+        <v>0.2233134723673889</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2972211554426338</v>
+        <v>0.2941882865095458</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2515952322270935</v>
+        <v>0.2534952322270935</v>
       </c>
       <c r="C100">
-        <v>-523.2642436592826</v>
+        <v>-533.8826978999751</v>
       </c>
       <c r="D100">
-        <v>246.0017563407175</v>
+        <v>244.1503021000248</v>
       </c>
       <c r="E100">
-        <v>843.1660000000001</v>
+        <v>851.933</v>
       </c>
       <c r="F100">
-        <v>859.1660000000001</v>
+        <v>867.933</v>
       </c>
       <c r="G100">
         <v>89.90000000000001</v>
@@ -9487,37 +9487,37 @@
         <v>59.59999999999999</v>
       </c>
       <c r="M100">
-        <v>202.5913428</v>
+        <v>204.6586014</v>
       </c>
       <c r="N100">
-        <v>-142.9913428</v>
+        <v>-145.0586014</v>
       </c>
       <c r="O100">
-        <v>-25.738441704</v>
+        <v>-26.110548252</v>
       </c>
       <c r="P100">
-        <v>-117.252901096</v>
+        <v>-118.948053148</v>
       </c>
       <c r="Q100">
-        <v>-85.25290109600002</v>
+        <v>-86.94805314800001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.637401465352619</v>
+        <v>3.229002930705238</v>
       </c>
       <c r="T100">
-        <v>26.83668723490302</v>
+        <v>53.67337446980604</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05295389157171822</v>
+        <v>0.05241900377806451</v>
       </c>
       <c r="W100">
-        <v>0.2233134723673889</v>
+        <v>0.2234395989091324</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2941882865095458</v>
+        <v>0.2912166876559139</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2534952322270935</v>
-      </c>
-      <c r="C101">
-        <v>-533.8826978999751</v>
-      </c>
-      <c r="D101">
-        <v>244.1503021000248</v>
-      </c>
-      <c r="E101">
-        <v>851.933</v>
-      </c>
-      <c r="F101">
-        <v>867.933</v>
-      </c>
-      <c r="G101">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="H101">
-        <v>860.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="K101">
-        <v>32</v>
-      </c>
-      <c r="L101">
-        <v>59.59999999999999</v>
-      </c>
-      <c r="M101">
-        <v>204.6586014</v>
-      </c>
-      <c r="N101">
-        <v>-145.0586014</v>
-      </c>
-      <c r="O101">
-        <v>-26.110548252</v>
-      </c>
-      <c r="P101">
-        <v>-118.948053148</v>
-      </c>
-      <c r="Q101">
-        <v>-86.94805314800001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.229002930705238</v>
-      </c>
-      <c r="T101">
-        <v>53.67337446980604</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05241900377806451</v>
-      </c>
-      <c r="W101">
-        <v>0.2234395989091324</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2912166876559139</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
